--- a/src/inventory/Mir.xlsx
+++ b/src/inventory/Mir.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="972">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -1229,660 +1229,669 @@
     <t>৳350.00</t>
   </si>
   <si>
+    <t>৳790.00</t>
+  </si>
+  <si>
+    <t>৳2,596.00</t>
+  </si>
+  <si>
+    <t>110-0101-013</t>
+  </si>
+  <si>
+    <t>Maroon Trousers</t>
+  </si>
+  <si>
+    <t>৳328.46</t>
+  </si>
+  <si>
+    <t>৳4,270.00</t>
+  </si>
+  <si>
+    <t>৳12,974.00</t>
+  </si>
+  <si>
+    <t>109-0102-063</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 063</t>
+  </si>
+  <si>
+    <t>৳1,050.00</t>
+  </si>
+  <si>
+    <t>৳2,850.00</t>
+  </si>
+  <si>
+    <t>109-0102-064</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 064</t>
+  </si>
+  <si>
+    <t>109-0102-070</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 070</t>
+  </si>
+  <si>
     <t>৳700.00</t>
   </si>
   <si>
+    <t>৳1,500.00</t>
+  </si>
+  <si>
+    <t>109-0102-071</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 071</t>
+  </si>
+  <si>
+    <t>৳3,000.00</t>
+  </si>
+  <si>
+    <t>৳305.82</t>
+  </si>
+  <si>
+    <t>৳5,810.67</t>
+  </si>
+  <si>
+    <t>৳18,962.00</t>
+  </si>
+  <si>
+    <t>105-0202-005</t>
+  </si>
+  <si>
+    <t>Choco Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>Men / 10% OFF,NEW IN,SALE,NEW,MEN,TURTLE-NECK</t>
+  </si>
+  <si>
+    <t>৳310.00</t>
+  </si>
+  <si>
+    <t>৳698.00</t>
+  </si>
+  <si>
+    <t>৳255.10</t>
+  </si>
+  <si>
+    <t>৳765.31</t>
+  </si>
+  <si>
+    <t>৳3,780.00</t>
+  </si>
+  <si>
+    <t>৳305.13</t>
+  </si>
+  <si>
+    <t>105-0202-004</t>
+  </si>
+  <si>
+    <t>Light Ash Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>৳1,396.00</t>
+  </si>
+  <si>
+    <t>105-0201-028</t>
+  </si>
+  <si>
+    <t>Full Sleeve Sea-Green Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,FULL SLEEVE</t>
+  </si>
+  <si>
+    <t>৳322.08</t>
+  </si>
+  <si>
+    <t>৳3,220.80</t>
+  </si>
+  <si>
+    <t>৳7,280.00</t>
+  </si>
+  <si>
+    <t>105-0202-003</t>
+  </si>
+  <si>
+    <t>Sky Blue Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>৳3,410.00</t>
+  </si>
+  <si>
+    <t>৳7,678.00</t>
+  </si>
+  <si>
+    <t>৳320.00</t>
+  </si>
+  <si>
+    <t>৳2,240.00</t>
+  </si>
+  <si>
+    <t>৳5,096.00</t>
+  </si>
+  <si>
+    <t>৳6,720.00</t>
+  </si>
+  <si>
+    <t>৳15,288.00</t>
+  </si>
+  <si>
+    <t>৳3,840.00</t>
+  </si>
+  <si>
+    <t>৳8,736.00</t>
+  </si>
+  <si>
+    <t>৳2,880.00</t>
+  </si>
+  <si>
+    <t>৳6,552.00</t>
+  </si>
+  <si>
+    <t>৳6,282.00</t>
+  </si>
+  <si>
+    <t>৳288.02</t>
+  </si>
+  <si>
+    <t>৳1,728.11</t>
+  </si>
+  <si>
+    <t>৳7,560.00</t>
+  </si>
+  <si>
+    <t>109-0103-003</t>
+  </si>
+  <si>
+    <t>DEEN Trifold Genuine Leather Wallet</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,WALLET,TRI-FOLD</t>
+  </si>
+  <si>
+    <t>৳1,698.00</t>
+  </si>
+  <si>
+    <t>৳2,170.00</t>
+  </si>
+  <si>
+    <t>৳4,886.00</t>
+  </si>
+  <si>
+    <t>৳214.46</t>
+  </si>
+  <si>
+    <t>৳857.84</t>
+  </si>
+  <si>
+    <t>105-0202-002</t>
+  </si>
+  <si>
+    <t>White Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>105-0301-007</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 07</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Men / Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳7,700.00</t>
+  </si>
+  <si>
+    <t>৳11,060.00</t>
+  </si>
+  <si>
+    <t>101-0100-139</t>
+  </si>
+  <si>
+    <t>Slim Fit Original Blue Jeans</t>
+  </si>
+  <si>
+    <t>৳1,790.00</t>
+  </si>
+  <si>
+    <t>109-0102-069</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 069</t>
+  </si>
+  <si>
+    <t>৳850.00</t>
+  </si>
+  <si>
+    <t>107-0100-052</t>
+  </si>
+  <si>
+    <t>Navy Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 15% OFF,SALE,MEN,BOXER,BRIEFS</t>
+  </si>
+  <si>
+    <t>৳277.76</t>
+  </si>
+  <si>
+    <t>৳1,666.56</t>
+  </si>
+  <si>
+    <t>৳2,094.00</t>
+  </si>
+  <si>
+    <t>1105-0301-001</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>৳493.71</t>
+  </si>
+  <si>
+    <t>৳8,886.73</t>
+  </si>
+  <si>
+    <t>৳15,120.00</t>
+  </si>
+  <si>
+    <t>৳90.91</t>
+  </si>
+  <si>
+    <t>109-0104-001</t>
+  </si>
+  <si>
+    <t>Card Holder 001</t>
+  </si>
+  <si>
+    <t>৳1,770.00</t>
+  </si>
+  <si>
+    <t>105-0301-009</t>
+  </si>
+  <si>
+    <t>Deep Violet Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>3XL</t>
+  </si>
+  <si>
+    <t>৳2,100.00</t>
+  </si>
+  <si>
+    <t>৳4,740.00</t>
+  </si>
+  <si>
+    <t>105-0301-006</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 06</t>
+  </si>
+  <si>
+    <t>৳4,200.00</t>
+  </si>
+  <si>
+    <t>৳277.78</t>
+  </si>
+  <si>
+    <t>107-0100-051</t>
+  </si>
+  <si>
+    <t>Cool Aqua Boxer Brief</t>
+  </si>
+  <si>
+    <t>৳263.33</t>
+  </si>
+  <si>
+    <t>৳2,370.00</t>
+  </si>
+  <si>
+    <t>৳3,141.00</t>
+  </si>
+  <si>
+    <t>109-0402-042</t>
+  </si>
+  <si>
+    <t>Leather Belt 042</t>
+  </si>
+  <si>
+    <t>৳515.62</t>
+  </si>
+  <si>
+    <t>৳7,218.75</t>
+  </si>
+  <si>
+    <t>109-0103-001</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳375.00</t>
+  </si>
+  <si>
+    <t>৳3,360.00</t>
+  </si>
+  <si>
+    <t>৳269.23</t>
+  </si>
+  <si>
+    <t>৳227.28</t>
+  </si>
+  <si>
+    <t>৳909.10</t>
+  </si>
+  <si>
+    <t>103-0200-100</t>
+  </si>
+  <si>
+    <t>Malibu Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>৳1,596.00</t>
+  </si>
+  <si>
+    <t>৳208.33</t>
+  </si>
+  <si>
+    <t>৳1,041.67</t>
+  </si>
+  <si>
+    <t>105-0301-008</t>
+  </si>
+  <si>
+    <t>Crew Graphic Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
     <t>৳1,580.00</t>
   </si>
   <si>
-    <t>৳2,596.00</t>
-  </si>
-  <si>
-    <t>110-0101-013</t>
-  </si>
-  <si>
-    <t>Maroon Trousers</t>
-  </si>
-  <si>
-    <t>৳328.46</t>
-  </si>
-  <si>
-    <t>৳4,270.00</t>
-  </si>
-  <si>
-    <t>৳12,974.00</t>
-  </si>
-  <si>
-    <t>109-0102-063</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 063</t>
-  </si>
-  <si>
-    <t>৳1,050.00</t>
-  </si>
-  <si>
-    <t>৳2,850.00</t>
-  </si>
-  <si>
-    <t>109-0102-064</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 064</t>
-  </si>
-  <si>
-    <t>109-0102-070</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 070</t>
-  </si>
-  <si>
-    <t>৳1,500.00</t>
-  </si>
-  <si>
-    <t>109-0102-071</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 071</t>
-  </si>
-  <si>
-    <t>৳3,000.00</t>
-  </si>
-  <si>
-    <t>৳305.82</t>
-  </si>
-  <si>
-    <t>৳5,810.67</t>
-  </si>
-  <si>
-    <t>৳18,962.00</t>
-  </si>
-  <si>
-    <t>105-0202-005</t>
-  </si>
-  <si>
-    <t>Choco Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>Men / 10% OFF,NEW IN,SALE,NEW,MEN,TURTLE-NECK</t>
-  </si>
-  <si>
-    <t>৳310.00</t>
-  </si>
-  <si>
-    <t>৳698.00</t>
-  </si>
-  <si>
-    <t>৳255.10</t>
-  </si>
-  <si>
-    <t>৳765.31</t>
-  </si>
-  <si>
-    <t>৳3,780.00</t>
-  </si>
-  <si>
-    <t>৳305.13</t>
-  </si>
-  <si>
-    <t>105-0202-004</t>
-  </si>
-  <si>
-    <t>Light Ash Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>৳1,396.00</t>
-  </si>
-  <si>
-    <t>105-0201-028</t>
-  </si>
-  <si>
-    <t>Full Sleeve Sea-Green Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,FULL SLEEVE</t>
-  </si>
-  <si>
-    <t>৳322.08</t>
-  </si>
-  <si>
-    <t>৳3,220.80</t>
-  </si>
-  <si>
-    <t>৳7,280.00</t>
-  </si>
-  <si>
-    <t>105-0202-003</t>
-  </si>
-  <si>
-    <t>Sky Blue Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>৳3,410.00</t>
-  </si>
-  <si>
-    <t>৳7,678.00</t>
-  </si>
-  <si>
-    <t>৳320.00</t>
-  </si>
-  <si>
-    <t>৳2,240.00</t>
-  </si>
-  <si>
-    <t>৳5,096.00</t>
-  </si>
-  <si>
-    <t>৳6,720.00</t>
-  </si>
-  <si>
-    <t>৳15,288.00</t>
-  </si>
-  <si>
-    <t>৳3,840.00</t>
-  </si>
-  <si>
-    <t>৳8,736.00</t>
-  </si>
-  <si>
-    <t>৳2,880.00</t>
-  </si>
-  <si>
-    <t>৳6,552.00</t>
-  </si>
-  <si>
-    <t>৳6,282.00</t>
-  </si>
-  <si>
-    <t>৳288.02</t>
-  </si>
-  <si>
-    <t>৳1,728.11</t>
-  </si>
-  <si>
-    <t>৳7,560.00</t>
-  </si>
-  <si>
-    <t>109-0103-003</t>
-  </si>
-  <si>
-    <t>DEEN Trifold Genuine Leather Wallet</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WALLET,TRI-FOLD</t>
-  </si>
-  <si>
-    <t>৳1,698.00</t>
-  </si>
-  <si>
-    <t>৳2,170.00</t>
-  </si>
-  <si>
-    <t>৳4,886.00</t>
-  </si>
-  <si>
-    <t>৳214.46</t>
-  </si>
-  <si>
-    <t>৳857.84</t>
-  </si>
-  <si>
-    <t>105-0202-002</t>
-  </si>
-  <si>
-    <t>White Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>105-0301-007</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 07</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Men / Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳7,700.00</t>
-  </si>
-  <si>
-    <t>৳11,060.00</t>
-  </si>
-  <si>
-    <t>101-0100-139</t>
-  </si>
-  <si>
-    <t>Slim Fit Original Blue Jeans</t>
-  </si>
-  <si>
-    <t>৳1,790.00</t>
-  </si>
-  <si>
-    <t>109-0102-069</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 069</t>
+    <t>৳209.79</t>
+  </si>
+  <si>
+    <t>৳2,727.30</t>
+  </si>
+  <si>
+    <t>৳250.00</t>
+  </si>
+  <si>
+    <t>105-0301-005</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 05</t>
+  </si>
+  <si>
+    <t>৳488.89</t>
+  </si>
+  <si>
+    <t>৳7,822.22</t>
+  </si>
+  <si>
+    <t>৳12,640.00</t>
+  </si>
+  <si>
+    <t>৳415.24</t>
+  </si>
+  <si>
+    <t>৳3,737.12</t>
+  </si>
+  <si>
+    <t>৳7,110.00</t>
+  </si>
+  <si>
+    <t>৳1,680.00</t>
+  </si>
+  <si>
+    <t>109-0102-074</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 74</t>
+  </si>
+  <si>
+    <t>Men / WALLET,BI-FOLD</t>
+  </si>
+  <si>
+    <t>৳2,097.00</t>
+  </si>
+  <si>
+    <t>109-0402-054</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 54</t>
+  </si>
+  <si>
+    <t>৳3,300.00</t>
+  </si>
+  <si>
+    <t>৳5,700.00</t>
+  </si>
+  <si>
+    <t>109-0402-057</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 57</t>
+  </si>
+  <si>
+    <t>৳233.33</t>
+  </si>
+  <si>
+    <t>৳4,188.00</t>
+  </si>
+  <si>
+    <t>৳175.00</t>
+  </si>
+  <si>
+    <t>৳3,160.00</t>
+  </si>
+  <si>
+    <t>109-0104-002</t>
+  </si>
+  <si>
+    <t>Card Holder 002</t>
+  </si>
+  <si>
+    <t>109-0104-003</t>
+  </si>
+  <si>
+    <t>Card Holder 003</t>
+  </si>
+  <si>
+    <t>৳2,360.00</t>
+  </si>
+  <si>
+    <t>102-0302-045</t>
+  </si>
+  <si>
+    <t>Rustic Tartan Flannel Shirt</t>
+  </si>
+  <si>
+    <t>Men / MEN,SHIRT,CASUAL SHIRT,FULL SLEEVE,FLANNEL SHIRT</t>
+  </si>
+  <si>
+    <t>৳349.00</t>
+  </si>
+  <si>
+    <t>৳218.75</t>
+  </si>
+  <si>
+    <t>৳656.25</t>
+  </si>
+  <si>
+    <t>109-0104-004</t>
+  </si>
+  <si>
+    <t>Card Holder 004</t>
+  </si>
+  <si>
+    <t>৳25.00</t>
+  </si>
+  <si>
+    <t>105-0301-001</t>
+  </si>
+  <si>
+    <t>৳504.17</t>
+  </si>
+  <si>
+    <t>৳5,545.83</t>
+  </si>
+  <si>
+    <t>৳9,240.00</t>
+  </si>
+  <si>
+    <t>109-0402-051</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 51</t>
+  </si>
+  <si>
+    <t>৳116.67</t>
+  </si>
+  <si>
+    <t>109-0102-073</t>
+  </si>
+  <si>
+    <t>Bifold Leather Wallet 73</t>
+  </si>
+  <si>
+    <t>৳4,194.00</t>
+  </si>
+  <si>
+    <t>109-0402-048</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 48</t>
+  </si>
+  <si>
+    <t>৳2,250.00</t>
+  </si>
+  <si>
+    <t>105-0201-037</t>
+  </si>
+  <si>
+    <t>Full Sleeve Side-Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>৳337.20</t>
+  </si>
+  <si>
+    <t>৳1,348.80</t>
+  </si>
+  <si>
+    <t>৳2,912.00</t>
+  </si>
+  <si>
+    <t>৳214.93</t>
+  </si>
+  <si>
+    <t>৳1,074.67</t>
+  </si>
+  <si>
+    <t>৳3,490.00</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>৳3,950.00</t>
+  </si>
+  <si>
+    <t>109-0502-001</t>
+  </si>
+  <si>
+    <t>Breathable Face Mask</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,MASK</t>
+  </si>
+  <si>
+    <t>৳223.83</t>
+  </si>
+  <si>
+    <t>৳895.32</t>
+  </si>
+  <si>
+    <t>৳1,120.00</t>
+  </si>
+  <si>
+    <t>105-0201-033</t>
+  </si>
+  <si>
+    <t>Full Sleeve Neon Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>৳3,640.00</t>
+  </si>
+  <si>
+    <t>109-0402-050</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 50</t>
+  </si>
+  <si>
+    <t>৳2,970.00</t>
+  </si>
+  <si>
+    <t>109-0102-072</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 72</t>
+  </si>
+  <si>
+    <t>৳2,450.00</t>
+  </si>
+  <si>
+    <t>৳4,893.00</t>
+  </si>
+  <si>
+    <t>109-0402-056</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 56</t>
+  </si>
+  <si>
+    <t>৳3,800.00</t>
+  </si>
+  <si>
+    <t>৳4,400.00</t>
+  </si>
+  <si>
+    <t>103-0200-098</t>
+  </si>
+  <si>
+    <t>White Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>৳2,394.00</t>
+  </si>
+  <si>
+    <t>109-0101-051</t>
+  </si>
+  <si>
+    <t>Leather Zipper Long Wallet 51</t>
+  </si>
+  <si>
+    <t>Men / WALLET,LONG</t>
   </si>
   <si>
     <t>৳900.00</t>
   </si>
   <si>
-    <t>107-0100-052</t>
-  </si>
-  <si>
-    <t>Navy Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 15% OFF,SALE,MEN,BOXER,BRIEFS</t>
-  </si>
-  <si>
-    <t>৳277.76</t>
-  </si>
-  <si>
-    <t>৳1,666.56</t>
-  </si>
-  <si>
-    <t>৳2,094.00</t>
-  </si>
-  <si>
-    <t>1105-0301-001</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>৳493.71</t>
-  </si>
-  <si>
-    <t>৳8,886.73</t>
-  </si>
-  <si>
-    <t>৳15,120.00</t>
-  </si>
-  <si>
-    <t>৳90.91</t>
-  </si>
-  <si>
-    <t>109-0104-001</t>
-  </si>
-  <si>
-    <t>Card Holder 001</t>
-  </si>
-  <si>
-    <t>৳1,770.00</t>
-  </si>
-  <si>
-    <t>105-0301-009</t>
-  </si>
-  <si>
-    <t>Deep Violet Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>3XL</t>
-  </si>
-  <si>
-    <t>৳2,100.00</t>
-  </si>
-  <si>
-    <t>৳4,740.00</t>
-  </si>
-  <si>
-    <t>105-0301-006</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 06</t>
-  </si>
-  <si>
-    <t>৳4,200.00</t>
-  </si>
-  <si>
-    <t>৳277.78</t>
-  </si>
-  <si>
-    <t>107-0100-051</t>
-  </si>
-  <si>
-    <t>Cool Aqua Boxer Brief</t>
-  </si>
-  <si>
-    <t>৳263.33</t>
-  </si>
-  <si>
-    <t>৳2,370.00</t>
-  </si>
-  <si>
-    <t>৳3,141.00</t>
-  </si>
-  <si>
-    <t>109-0402-042</t>
-  </si>
-  <si>
-    <t>Leather Belt 042</t>
-  </si>
-  <si>
-    <t>৳515.62</t>
-  </si>
-  <si>
-    <t>৳7,218.75</t>
-  </si>
-  <si>
-    <t>109-0103-001</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳375.00</t>
-  </si>
-  <si>
-    <t>৳3,360.00</t>
-  </si>
-  <si>
-    <t>৳269.23</t>
-  </si>
-  <si>
-    <t>৳227.28</t>
-  </si>
-  <si>
-    <t>৳909.10</t>
-  </si>
-  <si>
-    <t>103-0200-100</t>
-  </si>
-  <si>
-    <t>Malibu Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>৳1,596.00</t>
-  </si>
-  <si>
-    <t>৳208.33</t>
-  </si>
-  <si>
-    <t>৳1,041.67</t>
-  </si>
-  <si>
-    <t>105-0301-008</t>
-  </si>
-  <si>
-    <t>Crew Graphic Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>৳209.79</t>
-  </si>
-  <si>
-    <t>৳2,727.30</t>
-  </si>
-  <si>
-    <t>৳250.00</t>
-  </si>
-  <si>
-    <t>105-0301-005</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 05</t>
-  </si>
-  <si>
-    <t>৳488.89</t>
-  </si>
-  <si>
-    <t>৳7,822.22</t>
-  </si>
-  <si>
-    <t>৳12,640.00</t>
-  </si>
-  <si>
-    <t>৳415.24</t>
-  </si>
-  <si>
-    <t>৳3,737.12</t>
-  </si>
-  <si>
-    <t>৳7,110.00</t>
-  </si>
-  <si>
-    <t>৳1,680.00</t>
-  </si>
-  <si>
-    <t>109-0102-074</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 74</t>
-  </si>
-  <si>
-    <t>Men / WALLET,BI-FOLD</t>
-  </si>
-  <si>
-    <t>৳2,097.00</t>
-  </si>
-  <si>
-    <t>109-0402-054</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 54</t>
-  </si>
-  <si>
-    <t>৳3,300.00</t>
-  </si>
-  <si>
-    <t>৳5,700.00</t>
-  </si>
-  <si>
-    <t>109-0402-057</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 57</t>
-  </si>
-  <si>
-    <t>৳233.33</t>
-  </si>
-  <si>
-    <t>৳4,188.00</t>
-  </si>
-  <si>
-    <t>৳175.00</t>
-  </si>
-  <si>
-    <t>৳3,160.00</t>
-  </si>
-  <si>
-    <t>109-0104-002</t>
-  </si>
-  <si>
-    <t>Card Holder 002</t>
-  </si>
-  <si>
-    <t>109-0104-003</t>
-  </si>
-  <si>
-    <t>Card Holder 003</t>
-  </si>
-  <si>
-    <t>৳2,360.00</t>
-  </si>
-  <si>
-    <t>102-0302-045</t>
-  </si>
-  <si>
-    <t>Rustic Tartan Flannel Shirt</t>
-  </si>
-  <si>
-    <t>Men / MEN,SHIRT,CASUAL SHIRT,FULL SLEEVE,FLANNEL SHIRT</t>
-  </si>
-  <si>
-    <t>৳349.00</t>
-  </si>
-  <si>
-    <t>৳218.75</t>
-  </si>
-  <si>
-    <t>৳656.25</t>
-  </si>
-  <si>
-    <t>109-0104-004</t>
-  </si>
-  <si>
-    <t>Card Holder 004</t>
-  </si>
-  <si>
-    <t>৳25.00</t>
-  </si>
-  <si>
-    <t>105-0301-001</t>
-  </si>
-  <si>
-    <t>৳504.17</t>
-  </si>
-  <si>
-    <t>৳5,545.83</t>
-  </si>
-  <si>
-    <t>৳9,240.00</t>
-  </si>
-  <si>
-    <t>109-0402-051</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 51</t>
-  </si>
-  <si>
-    <t>৳116.67</t>
-  </si>
-  <si>
-    <t>109-0102-073</t>
-  </si>
-  <si>
-    <t>Bifold Leather Wallet 73</t>
-  </si>
-  <si>
-    <t>৳4,194.00</t>
-  </si>
-  <si>
-    <t>109-0402-048</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 48</t>
-  </si>
-  <si>
-    <t>৳2,250.00</t>
-  </si>
-  <si>
-    <t>105-0201-037</t>
-  </si>
-  <si>
-    <t>Full Sleeve Side-Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>৳337.20</t>
-  </si>
-  <si>
-    <t>৳1,348.80</t>
-  </si>
-  <si>
-    <t>৳2,912.00</t>
-  </si>
-  <si>
-    <t>৳214.93</t>
-  </si>
-  <si>
-    <t>৳1,074.67</t>
-  </si>
-  <si>
-    <t>৳3,490.00</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>৳3,950.00</t>
-  </si>
-  <si>
-    <t>109-0502-001</t>
-  </si>
-  <si>
-    <t>Breathable Face Mask</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,MASK</t>
-  </si>
-  <si>
-    <t>৳223.83</t>
-  </si>
-  <si>
-    <t>৳895.32</t>
-  </si>
-  <si>
-    <t>৳1,120.00</t>
-  </si>
-  <si>
-    <t>105-0201-033</t>
-  </si>
-  <si>
-    <t>Full Sleeve Neon Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>৳3,640.00</t>
-  </si>
-  <si>
-    <t>109-0402-050</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 50</t>
-  </si>
-  <si>
-    <t>109-0102-072</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 72</t>
-  </si>
-  <si>
-    <t>৳2,450.00</t>
-  </si>
-  <si>
-    <t>৳4,893.00</t>
-  </si>
-  <si>
-    <t>109-0402-056</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 56</t>
-  </si>
-  <si>
-    <t>৳3,800.00</t>
-  </si>
-  <si>
-    <t>৳4,400.00</t>
-  </si>
-  <si>
-    <t>103-0200-098</t>
-  </si>
-  <si>
-    <t>White Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>৳2,394.00</t>
-  </si>
-  <si>
-    <t>109-0101-051</t>
-  </si>
-  <si>
-    <t>Leather Zipper Long Wallet 51</t>
-  </si>
-  <si>
-    <t>Men / WALLET,LONG</t>
-  </si>
-  <si>
     <t>৳2,698.00</t>
   </si>
   <si>
@@ -1976,6 +1985,9 @@
     <t>৳13,430.00</t>
   </si>
   <si>
+    <t>৳525.00</t>
+  </si>
+  <si>
     <t>109-0501-001</t>
   </si>
   <si>
@@ -2243,324 +2255,327 @@
     <t>৳2,160.00</t>
   </si>
   <si>
+    <t>৳1,905.56</t>
+  </si>
+  <si>
+    <t>৳4,130.00</t>
+  </si>
+  <si>
+    <t>105-0101-378</t>
+  </si>
+  <si>
+    <t>Mocha Rock T-shirt</t>
+  </si>
+  <si>
+    <t>৳640.00</t>
+  </si>
+  <si>
+    <t>105-0101-380</t>
+  </si>
+  <si>
+    <t>Essential Black T-shirt</t>
+  </si>
+  <si>
+    <t>৳5,900.00</t>
+  </si>
+  <si>
+    <t>108-0101-013</t>
+  </si>
+  <si>
+    <t>Brown Sweatshirt in French-Terry</t>
+  </si>
+  <si>
+    <t>৳10.58</t>
+  </si>
+  <si>
+    <t>৳74.08</t>
+  </si>
+  <si>
+    <t>৳269.56</t>
+  </si>
+  <si>
+    <t>৳1,886.90</t>
+  </si>
+  <si>
+    <t>106-0101-113</t>
+  </si>
+  <si>
+    <t>Motif Printed Semi Formal Panjabi</t>
+  </si>
+  <si>
+    <t>৳214.29</t>
+  </si>
+  <si>
+    <t>109-0402-053</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 53</t>
+  </si>
+  <si>
+    <t>৳1,980.00</t>
+  </si>
+  <si>
+    <t>109-0402-055</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 55</t>
+  </si>
+  <si>
+    <t>৳366.67</t>
+  </si>
+  <si>
+    <t>৳733.33</t>
+  </si>
+  <si>
+    <t>105-0401-004</t>
+  </si>
+  <si>
+    <t>Orlando Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
+    <t>105-0401-009</t>
+  </si>
+  <si>
+    <t>Gravity Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳178.57</t>
+  </si>
+  <si>
+    <t>৳1,166.67</t>
+  </si>
+  <si>
+    <t>৳64.89</t>
+  </si>
+  <si>
+    <t>৳194.67</t>
+  </si>
+  <si>
+    <t>৳2,844.00</t>
+  </si>
+  <si>
+    <t>102-0302-010</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 010</t>
+  </si>
+  <si>
+    <t>105-0401-008</t>
+  </si>
+  <si>
+    <t>White Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>102-0302-004</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 004</t>
+  </si>
+  <si>
+    <t>৳666.67</t>
+  </si>
+  <si>
+    <t>102-0302-007</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 007</t>
+  </si>
+  <si>
+    <t>৳2,650.00</t>
+  </si>
+  <si>
+    <t>৳4,350.00</t>
+  </si>
+  <si>
+    <t>105-0101-376</t>
+  </si>
+  <si>
+    <t>City Slate T-shirt</t>
+  </si>
+  <si>
+    <t>৳1,920.00</t>
+  </si>
+  <si>
+    <t>105-0401-001</t>
+  </si>
+  <si>
+    <t>Black Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>105-0101-377</t>
+  </si>
+  <si>
+    <t>Warm Spice T-shirt</t>
+  </si>
+  <si>
+    <t>৳87.50</t>
+  </si>
+  <si>
+    <t>105-0201-035</t>
+  </si>
+  <si>
+    <t>Full Sleeve Maroon Panel T-shirt</t>
+  </si>
+  <si>
+    <t>৳150.00</t>
+  </si>
+  <si>
+    <t>৳728.00</t>
+  </si>
+  <si>
+    <t>৳3,540.00</t>
+  </si>
+  <si>
+    <t>৳5,800.00</t>
+  </si>
+  <si>
+    <t>109-0101-045</t>
+  </si>
+  <si>
+    <t>Burgendy Leather Long Wallet</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
+  </si>
+  <si>
+    <t>৳1,299.00</t>
+  </si>
+  <si>
+    <t>109-0402-059</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 059</t>
+  </si>
+  <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
+    <t>1105-0401-001</t>
+  </si>
+  <si>
+    <t>৳7,680.00</t>
+  </si>
+  <si>
+    <t>৳200.00</t>
+  </si>
+  <si>
+    <t>৳50.00</t>
+  </si>
+  <si>
+    <t>৳204.55</t>
+  </si>
+  <si>
+    <t>৳6,490.00</t>
+  </si>
+  <si>
+    <t>102-0302-003</t>
+  </si>
+  <si>
+    <t>Cuban Shier 003</t>
+  </si>
+  <si>
+    <t>৳1,325.00</t>
+  </si>
+  <si>
+    <t>105-0202-006</t>
+  </si>
+  <si>
+    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>৳83.86</t>
+  </si>
+  <si>
+    <t>৳670.85</t>
+  </si>
+  <si>
+    <t>৳5,120.00</t>
+  </si>
+  <si>
+    <t>105-0201-034</t>
+  </si>
+  <si>
+    <t>Full Sleeve Mustard StripeT-shirt</t>
+  </si>
+  <si>
+    <t>৳4,368.00</t>
+  </si>
+  <si>
+    <t>102-0501-001</t>
+  </si>
+  <si>
+    <t>Formal Shirt 001</t>
+  </si>
+  <si>
+    <t>Men / SHIRT,FORMAL SHIRT</t>
+  </si>
+  <si>
+    <t>৳7,140.00</t>
+  </si>
+  <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>105-0101-371</t>
+  </si>
+  <si>
+    <t>Green Essence T-shirt</t>
+  </si>
+  <si>
+    <t>105-0101-374</t>
+  </si>
+  <si>
+    <t>Golden Corn T-shirt</t>
+  </si>
+  <si>
+    <t>৳212.33</t>
+  </si>
+  <si>
+    <t>৳424.66</t>
+  </si>
+  <si>
+    <t>৳166.67</t>
+  </si>
+  <si>
+    <t>৳833.33</t>
+  </si>
+  <si>
+    <t>102-0301-008</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 008</t>
+  </si>
+  <si>
+    <t>৳1,450.00</t>
+  </si>
+  <si>
+    <t>৳2,184.00</t>
+  </si>
+  <si>
+    <t>৳178.49</t>
+  </si>
+  <si>
+    <t>৳535.48</t>
+  </si>
+  <si>
+    <t>৳540.00</t>
+  </si>
+  <si>
+    <t>৳100.00</t>
+  </si>
+  <si>
+    <t>৳5,310.00</t>
+  </si>
+  <si>
     <t>৳4,720.00</t>
   </si>
   <si>
-    <t>105-0101-378</t>
-  </si>
-  <si>
-    <t>Mocha Rock T-shirt</t>
-  </si>
-  <si>
-    <t>৳640.00</t>
-  </si>
-  <si>
-    <t>105-0101-380</t>
-  </si>
-  <si>
-    <t>Essential Black T-shirt</t>
-  </si>
-  <si>
-    <t>৳5,900.00</t>
-  </si>
-  <si>
-    <t>108-0101-013</t>
-  </si>
-  <si>
-    <t>Brown Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>৳10.58</t>
-  </si>
-  <si>
-    <t>৳74.08</t>
-  </si>
-  <si>
-    <t>৳269.56</t>
-  </si>
-  <si>
-    <t>৳1,886.90</t>
-  </si>
-  <si>
-    <t>106-0101-113</t>
-  </si>
-  <si>
-    <t>Motif Printed Semi Formal Panjabi</t>
-  </si>
-  <si>
-    <t>৳214.29</t>
-  </si>
-  <si>
-    <t>109-0402-053</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 53</t>
-  </si>
-  <si>
-    <t>৳1,980.00</t>
-  </si>
-  <si>
-    <t>109-0402-055</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 55</t>
-  </si>
-  <si>
-    <t>৳366.67</t>
-  </si>
-  <si>
-    <t>৳733.33</t>
-  </si>
-  <si>
-    <t>105-0401-004</t>
-  </si>
-  <si>
-    <t>Orlando Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳3,200.00</t>
-  </si>
-  <si>
-    <t>105-0401-009</t>
-  </si>
-  <si>
-    <t>Gravity Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳178.57</t>
-  </si>
-  <si>
-    <t>৳4,130.00</t>
-  </si>
-  <si>
-    <t>৳1,166.67</t>
-  </si>
-  <si>
-    <t>৳64.89</t>
-  </si>
-  <si>
-    <t>৳194.67</t>
-  </si>
-  <si>
-    <t>৳2,844.00</t>
-  </si>
-  <si>
-    <t>102-0302-010</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 010</t>
-  </si>
-  <si>
-    <t>105-0401-008</t>
-  </si>
-  <si>
-    <t>White Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>102-0302-004</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 004</t>
-  </si>
-  <si>
-    <t>৳666.67</t>
-  </si>
-  <si>
-    <t>102-0302-007</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 007</t>
-  </si>
-  <si>
-    <t>৳2,650.00</t>
-  </si>
-  <si>
-    <t>৳4,350.00</t>
-  </si>
-  <si>
-    <t>105-0101-376</t>
-  </si>
-  <si>
-    <t>City Slate T-shirt</t>
-  </si>
-  <si>
-    <t>৳1,920.00</t>
-  </si>
-  <si>
-    <t>105-0401-001</t>
-  </si>
-  <si>
-    <t>Black Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>105-0101-377</t>
-  </si>
-  <si>
-    <t>Warm Spice T-shirt</t>
-  </si>
-  <si>
-    <t>৳87.50</t>
-  </si>
-  <si>
-    <t>105-0201-035</t>
-  </si>
-  <si>
-    <t>Full Sleeve Maroon Panel T-shirt</t>
-  </si>
-  <si>
-    <t>৳150.00</t>
-  </si>
-  <si>
-    <t>৳728.00</t>
-  </si>
-  <si>
-    <t>৳3,540.00</t>
-  </si>
-  <si>
-    <t>৳5,800.00</t>
-  </si>
-  <si>
-    <t>109-0101-045</t>
-  </si>
-  <si>
-    <t>Burgendy Leather Long Wallet</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳1,299.00</t>
-  </si>
-  <si>
-    <t>109-0402-059</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 059</t>
-  </si>
-  <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
-    <t>1105-0401-001</t>
-  </si>
-  <si>
-    <t>৳7,680.00</t>
-  </si>
-  <si>
-    <t>৳200.00</t>
-  </si>
-  <si>
-    <t>৳50.00</t>
-  </si>
-  <si>
-    <t>৳204.55</t>
-  </si>
-  <si>
-    <t>৳6,490.00</t>
-  </si>
-  <si>
-    <t>102-0302-003</t>
-  </si>
-  <si>
-    <t>Cuban Shier 003</t>
-  </si>
-  <si>
-    <t>৳1,325.00</t>
-  </si>
-  <si>
-    <t>105-0202-006</t>
-  </si>
-  <si>
-    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>৳83.86</t>
-  </si>
-  <si>
-    <t>৳670.85</t>
-  </si>
-  <si>
-    <t>৳5,120.00</t>
-  </si>
-  <si>
-    <t>105-0201-034</t>
-  </si>
-  <si>
-    <t>Full Sleeve Mustard StripeT-shirt</t>
-  </si>
-  <si>
-    <t>৳4,368.00</t>
-  </si>
-  <si>
-    <t>102-0501-001</t>
-  </si>
-  <si>
-    <t>Formal Shirt 001</t>
-  </si>
-  <si>
-    <t>Men / SHIRT,FORMAL SHIRT</t>
-  </si>
-  <si>
-    <t>৳7,140.00</t>
-  </si>
-  <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
-    <t>105-0101-371</t>
-  </si>
-  <si>
-    <t>Green Essence T-shirt</t>
-  </si>
-  <si>
-    <t>105-0101-374</t>
-  </si>
-  <si>
-    <t>Golden Corn T-shirt</t>
-  </si>
-  <si>
-    <t>৳212.33</t>
-  </si>
-  <si>
-    <t>৳424.66</t>
-  </si>
-  <si>
-    <t>৳166.67</t>
-  </si>
-  <si>
-    <t>৳833.33</t>
-  </si>
-  <si>
-    <t>102-0301-008</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 008</t>
-  </si>
-  <si>
-    <t>৳1,450.00</t>
-  </si>
-  <si>
-    <t>৳2,184.00</t>
-  </si>
-  <si>
-    <t>৳178.49</t>
-  </si>
-  <si>
-    <t>৳535.48</t>
-  </si>
-  <si>
-    <t>৳540.00</t>
-  </si>
-  <si>
-    <t>৳100.00</t>
-  </si>
-  <si>
-    <t>৳5,310.00</t>
-  </si>
-  <si>
     <t>105-0201-030</t>
   </si>
   <si>
@@ -2810,7 +2825,7 @@
     <t>৳7,450.00</t>
   </si>
   <si>
-    <t>৳14,900.00</t>
+    <t>৳13,410.00</t>
   </si>
   <si>
     <t>৳4,470.00</t>
@@ -3255,7 +3270,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I532"/>
+  <dimension ref="A1:I530"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7445,16 +7460,16 @@
         <v>402</v>
       </c>
       <c r="F163">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G163" t="s">
         <v>403</v>
       </c>
       <c r="H163" t="s">
+        <v>403</v>
+      </c>
+      <c r="I163" t="s">
         <v>404</v>
-      </c>
-      <c r="I163" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7480,15 +7495,15 @@
         <v>102</v>
       </c>
       <c r="I164" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
+        <v>406</v>
+      </c>
+      <c r="B165" t="s">
         <v>407</v>
-      </c>
-      <c r="B165" t="s">
-        <v>408</v>
       </c>
       <c r="C165" t="s">
         <v>123</v>
@@ -7500,21 +7515,21 @@
         <v>13.0</v>
       </c>
       <c r="G165" t="s">
+        <v>408</v>
+      </c>
+      <c r="H165" t="s">
         <v>409</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
         <v>410</v>
-      </c>
-      <c r="I165" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
+        <v>411</v>
+      </c>
+      <c r="B166" t="s">
         <v>412</v>
-      </c>
-      <c r="B166" t="s">
-        <v>413</v>
       </c>
       <c r="E166" t="s">
         <v>257</v>
@@ -7526,18 +7541,18 @@
         <v>403</v>
       </c>
       <c r="H166" t="s">
+        <v>413</v>
+      </c>
+      <c r="I166" t="s">
         <v>414</v>
-      </c>
-      <c r="I166" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
+        <v>415</v>
+      </c>
+      <c r="B167" t="s">
         <v>416</v>
-      </c>
-      <c r="B167" t="s">
-        <v>417</v>
       </c>
       <c r="E167" t="s">
         <v>257</v>
@@ -7549,18 +7564,18 @@
         <v>403</v>
       </c>
       <c r="H167" t="s">
+        <v>413</v>
+      </c>
+      <c r="I167" t="s">
         <v>414</v>
-      </c>
-      <c r="I167" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
+        <v>417</v>
+      </c>
+      <c r="B168" t="s">
         <v>418</v>
-      </c>
-      <c r="B168" t="s">
-        <v>419</v>
       </c>
       <c r="E168" t="s">
         <v>257</v>
@@ -7572,7 +7587,7 @@
         <v>403</v>
       </c>
       <c r="H168" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I168" t="s">
         <v>420</v>
@@ -7603,10 +7618,10 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
+        <v>406</v>
+      </c>
+      <c r="B170" t="s">
         <v>407</v>
-      </c>
-      <c r="B170" t="s">
-        <v>408</v>
       </c>
       <c r="C170" t="s">
         <v>136</v>
@@ -8094,10 +8109,10 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
+        <v>406</v>
+      </c>
+      <c r="B189" t="s">
         <v>407</v>
-      </c>
-      <c r="B189" t="s">
-        <v>408</v>
       </c>
       <c r="C189" t="s">
         <v>151</v>
@@ -8207,16 +8222,16 @@
         <v>257</v>
       </c>
       <c r="F193">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G193" t="s">
         <v>258</v>
       </c>
       <c r="H193" t="s">
+        <v>258</v>
+      </c>
+      <c r="I193" t="s">
         <v>483</v>
-      </c>
-      <c r="I193" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -8314,7 +8329,7 @@
         <v>403</v>
       </c>
       <c r="H197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I197" t="s">
         <v>498</v>
@@ -8646,10 +8661,10 @@
         <v>403</v>
       </c>
       <c r="H210" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I210" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -8669,10 +8684,10 @@
         <v>13.0</v>
       </c>
       <c r="G211" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H211" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I211" t="s">
         <v>357</v>
@@ -8695,7 +8710,7 @@
         <v>6.0</v>
       </c>
       <c r="G212" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H212" t="s">
         <v>420</v>
@@ -8706,10 +8721,10 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B213" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C213" t="s">
         <v>401</v>
@@ -8721,21 +8736,21 @@
         <v>16.0</v>
       </c>
       <c r="G213" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H213" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I213" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B214" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C214" t="s">
         <v>474</v>
@@ -8747,13 +8762,13 @@
         <v>9.0</v>
       </c>
       <c r="G214" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H214" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I214" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -8779,18 +8794,18 @@
         <v>149</v>
       </c>
       <c r="I215" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B216" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E216" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F216">
         <v>3.0</v>
@@ -8799,18 +8814,18 @@
         <v>403</v>
       </c>
       <c r="H216" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I216" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B217" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E217" t="s">
         <v>284</v>
@@ -8822,18 +8837,18 @@
         <v>148</v>
       </c>
       <c r="H217" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I217" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B218" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E218" t="s">
         <v>284</v>
@@ -8848,7 +8863,7 @@
         <v>32</v>
       </c>
       <c r="I218" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -8868,13 +8883,13 @@
         <v>6.0</v>
       </c>
       <c r="G219" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H219" t="s">
         <v>155</v>
       </c>
       <c r="I219" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -8894,21 +8909,21 @@
         <v>4.0</v>
       </c>
       <c r="G220" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H220" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I220" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B221" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E221" t="s">
         <v>257</v>
@@ -8920,7 +8935,7 @@
         <v>403</v>
       </c>
       <c r="H221" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I221" t="s">
         <v>498</v>
@@ -8928,10 +8943,10 @@
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B222" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E222" t="s">
         <v>257</v>
@@ -8946,21 +8961,21 @@
         <v>155</v>
       </c>
       <c r="I222" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B223" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C223" t="s">
         <v>128</v>
       </c>
       <c r="E223" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F223">
         <v>1.0</v>
@@ -8992,13 +9007,13 @@
         <v>1.0</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I224" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -9018,10 +9033,10 @@
         <v>3.0</v>
       </c>
       <c r="G225" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H225" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I225" t="s">
         <v>342</v>
@@ -9029,10 +9044,10 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B226" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E226" t="s">
         <v>257</v>
@@ -9044,7 +9059,7 @@
         <v>403</v>
       </c>
       <c r="H226" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I226" t="s">
         <v>498</v>
@@ -9067,10 +9082,10 @@
         <v>1.0</v>
       </c>
       <c r="G227" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H227" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I227" t="s">
         <v>322</v>
@@ -9078,7 +9093,7 @@
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B228" t="s">
         <v>491</v>
@@ -9093,21 +9108,21 @@
         <v>11.0</v>
       </c>
       <c r="G228" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H228" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I228" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B229" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E229" t="s">
         <v>284</v>
@@ -9142,24 +9157,24 @@
         <v>2.0</v>
       </c>
       <c r="G230" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H230" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I230" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B231" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E231" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F231">
         <v>6.0</v>
@@ -9171,15 +9186,15 @@
         <v>502</v>
       </c>
       <c r="I231" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B232" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E232" t="s">
         <v>284</v>
@@ -9191,7 +9206,7 @@
         <v>258</v>
       </c>
       <c r="H232" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I232" t="s">
         <v>354</v>
@@ -9199,10 +9214,10 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B233" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C233" t="s">
         <v>151</v>
@@ -9214,13 +9229,13 @@
         <v>4.0</v>
       </c>
       <c r="G233" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H233" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I233" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -9240,13 +9255,13 @@
         <v>5.0</v>
       </c>
       <c r="G234" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H234" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I234" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9257,7 +9272,7 @@
         <v>473</v>
       </c>
       <c r="C235" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E235" t="s">
         <v>475</v>
@@ -9272,15 +9287,15 @@
         <v>353</v>
       </c>
       <c r="I235" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B236" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C236" t="s">
         <v>520</v>
@@ -9298,38 +9313,38 @@
         <v>354</v>
       </c>
       <c r="I236" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B237" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E237" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F237">
         <v>4.0</v>
       </c>
       <c r="G237" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H237" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I237" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B238" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C238" t="s">
         <v>151</v>
@@ -9347,41 +9362,41 @@
         <v>102</v>
       </c>
       <c r="I238" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B239" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E239" t="s">
         <v>284</v>
       </c>
       <c r="F239">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G239" t="s">
         <v>148</v>
       </c>
       <c r="H239" t="s">
-        <v>325</v>
+        <v>32</v>
       </c>
       <c r="I239" t="s">
-        <v>326</v>
+        <v>609</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B240" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E240" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F240">
         <v>7.0</v>
@@ -9390,18 +9405,18 @@
         <v>403</v>
       </c>
       <c r="H240" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I240" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B241" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E241" t="s">
         <v>284</v>
@@ -9416,12 +9431,12 @@
         <v>325</v>
       </c>
       <c r="I241" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B242" t="s">
         <v>491</v>
@@ -9439,7 +9454,7 @@
         <v>148</v>
       </c>
       <c r="H242" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I242" t="s">
         <v>452</v>
@@ -9447,10 +9462,10 @@
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B243" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C243" t="s">
         <v>128</v>
@@ -9468,18 +9483,18 @@
         <v>102</v>
       </c>
       <c r="I243" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B244" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E244" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F244">
         <v>2.0</v>
@@ -9488,10 +9503,10 @@
         <v>258</v>
       </c>
       <c r="H244" t="s">
-        <v>483</v>
+        <v>624</v>
       </c>
       <c r="I244" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -9514,21 +9529,21 @@
         <v>148</v>
       </c>
       <c r="H245" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I245" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B246" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C246" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E246" t="s">
         <v>475</v>
@@ -9540,10 +9555,10 @@
         <v>148</v>
       </c>
       <c r="H246" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I246" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -9563,10 +9578,10 @@
         <v>1.0</v>
       </c>
       <c r="G247" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H247" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="I247" t="s">
         <v>28</v>
@@ -9574,10 +9589,10 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B248" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C248" t="s">
         <v>123</v>
@@ -9589,13 +9604,13 @@
         <v>2.0</v>
       </c>
       <c r="G248" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H248" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="I248" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -9615,10 +9630,10 @@
         <v>5.0</v>
       </c>
       <c r="G249" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="H249" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="I249" t="s">
         <v>506</v>
@@ -9647,33 +9662,33 @@
         <v>149</v>
       </c>
       <c r="I250" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B251" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C251" t="s">
         <v>474</v>
       </c>
       <c r="E251" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F251">
         <v>7.0</v>
       </c>
       <c r="G251" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H251" t="s">
         <v>316</v>
       </c>
       <c r="I251" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -9704,13 +9719,13 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B253" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E253" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F253">
         <v>6.0</v>
@@ -9722,7 +9737,7 @@
         <v>280</v>
       </c>
       <c r="I253" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -9748,21 +9763,21 @@
         <v>280</v>
       </c>
       <c r="I254" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B255" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C255" t="s">
         <v>231</v>
       </c>
       <c r="E255" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F255">
         <v>1.0</v>
@@ -9774,7 +9789,7 @@
         <v>403</v>
       </c>
       <c r="I255" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -9794,21 +9809,21 @@
         <v>8.0</v>
       </c>
       <c r="G256" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H256" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I256" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B257" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E257" t="s">
         <v>284</v>
@@ -9823,15 +9838,15 @@
         <v>280</v>
       </c>
       <c r="I257" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B258" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C258" t="s">
         <v>128</v>
@@ -9843,10 +9858,10 @@
         <v>7.0</v>
       </c>
       <c r="G258" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H258" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I258" t="s">
         <v>451</v>
@@ -9869,13 +9884,13 @@
         <v>17.0</v>
       </c>
       <c r="G259" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="H259" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="I259" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -9918,53 +9933,53 @@
         <v>402</v>
       </c>
       <c r="F261">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G261" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H261" t="s">
-        <v>404</v>
+        <v>656</v>
       </c>
       <c r="I261" t="s">
-        <v>559</v>
+        <v>511</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B262" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E262" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F262">
         <v>2.0</v>
       </c>
       <c r="G262" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="H262" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I262" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B263" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C263" t="s">
         <v>401</v>
       </c>
       <c r="E263" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F263">
         <v>1.0</v>
@@ -9976,15 +9991,15 @@
         <v>102</v>
       </c>
       <c r="I263" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B264" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C264" t="s">
         <v>128</v>
@@ -10002,18 +10017,18 @@
         <v>102</v>
       </c>
       <c r="I264" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B265" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E265" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F265">
         <v>3.0</v>
@@ -10025,7 +10040,7 @@
         <v>62</v>
       </c>
       <c r="I265" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -10045,24 +10060,24 @@
         <v>4.0</v>
       </c>
       <c r="G266" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H266" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I266" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B267" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E267" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F267">
         <v>5.0</v>
@@ -10071,21 +10086,21 @@
         <v>403</v>
       </c>
       <c r="H267" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I267" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B268" t="s">
+        <v>678</v>
+      </c>
+      <c r="E268" t="s">
         <v>674</v>
-      </c>
-      <c r="E268" t="s">
-        <v>670</v>
       </c>
       <c r="F268">
         <v>4.0</v>
@@ -10097,18 +10112,18 @@
         <v>155</v>
       </c>
       <c r="I268" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B269" t="s">
         <v>491</v>
       </c>
       <c r="C269" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E269" t="s">
         <v>475</v>
@@ -10120,7 +10135,7 @@
         <v>148</v>
       </c>
       <c r="H269" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I269" t="s">
         <v>452</v>
@@ -10134,7 +10149,7 @@
         <v>500</v>
       </c>
       <c r="C270" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E270" t="s">
         <v>402</v>
@@ -10143,13 +10158,13 @@
         <v>8.0</v>
       </c>
       <c r="G270" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H270" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I270" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -10172,7 +10187,7 @@
         <v>403</v>
       </c>
       <c r="H271" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I271" t="s">
         <v>511</v>
@@ -10180,36 +10195,36 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B272" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C272" t="s">
         <v>474</v>
       </c>
       <c r="E272" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F272">
         <v>13.0</v>
       </c>
       <c r="G272" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="H272" t="s">
         <v>60</v>
       </c>
       <c r="I272" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B273" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C273">
         <v>40</v>
@@ -10227,73 +10242,73 @@
         <v>81</v>
       </c>
       <c r="I273" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B274" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C274" t="s">
         <v>474</v>
       </c>
       <c r="E274" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F274">
         <v>9.0</v>
       </c>
       <c r="G274" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H274" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I274" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B275" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C275" t="s">
         <v>401</v>
       </c>
       <c r="E275" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F275">
         <v>4.0</v>
       </c>
       <c r="G275" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H275" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I275" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B276" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C276" t="s">
         <v>501</v>
       </c>
       <c r="E276" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F276">
         <v>2.0</v>
@@ -10302,10 +10317,10 @@
         <v>403</v>
       </c>
       <c r="H276" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I276" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -10325,21 +10340,21 @@
         <v>5.0</v>
       </c>
       <c r="G277" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="H277" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="I277" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B278" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E278" t="s">
         <v>464</v>
@@ -10354,15 +10369,15 @@
         <v>102</v>
       </c>
       <c r="I278" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B279" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C279" t="s">
         <v>128</v>
@@ -10380,21 +10395,21 @@
         <v>102</v>
       </c>
       <c r="I279" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B280" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C280" t="s">
         <v>474</v>
       </c>
       <c r="E280" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F280">
         <v>2.0</v>
@@ -10406,18 +10421,18 @@
         <v>102</v>
       </c>
       <c r="I280" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B281" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E281" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F281">
         <v>4.0</v>
@@ -10429,47 +10444,47 @@
         <v>259</v>
       </c>
       <c r="I281" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B282" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C282" t="s">
         <v>474</v>
       </c>
       <c r="E282" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F282">
         <v>4.0</v>
       </c>
       <c r="G282" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H282" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="I282" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B283" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C283" t="s">
         <v>474</v>
       </c>
       <c r="E283" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F283">
         <v>6.0</v>
@@ -10481,38 +10496,38 @@
         <v>102</v>
       </c>
       <c r="I283" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B284" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C284" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E284" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F284">
         <v>7.0</v>
       </c>
       <c r="G284" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H284" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I284" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B285" t="s">
         <v>491</v>
@@ -10533,21 +10548,21 @@
         <v>148</v>
       </c>
       <c r="I285" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B286" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C286" t="s">
         <v>520</v>
       </c>
       <c r="E286" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F286">
         <v>6.0</v>
@@ -10559,67 +10574,67 @@
         <v>502</v>
       </c>
       <c r="I286" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B287" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C287" t="s">
         <v>474</v>
       </c>
       <c r="E287" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F287">
         <v>3.0</v>
       </c>
       <c r="G287" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="H287" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="I287" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B288" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C288" t="s">
         <v>401</v>
       </c>
       <c r="E288" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F288">
         <v>10.0</v>
       </c>
       <c r="G288" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="H288" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I288" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B289" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E289" t="s">
         <v>284</v>
@@ -10634,21 +10649,21 @@
         <v>280</v>
       </c>
       <c r="I289" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B290" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C290" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E290" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F290">
         <v>3.0</v>
@@ -10657,24 +10672,24 @@
         <v>389</v>
       </c>
       <c r="H290" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I290" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B291" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C291" t="s">
         <v>520</v>
       </c>
       <c r="E291" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F291">
         <v>1.0</v>
@@ -10686,21 +10701,21 @@
         <v>102</v>
       </c>
       <c r="I291" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B292" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C292" t="s">
         <v>474</v>
       </c>
       <c r="E292" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F292">
         <v>6.0</v>
@@ -10712,44 +10727,44 @@
         <v>102</v>
       </c>
       <c r="I292" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B293" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C293" t="s">
         <v>520</v>
       </c>
       <c r="E293" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F293">
         <v>4.0</v>
       </c>
       <c r="G293" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H293" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I293" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B294" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E294" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F294">
         <v>3.0</v>
@@ -10761,21 +10776,21 @@
         <v>62</v>
       </c>
       <c r="I294" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B295" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C295" t="s">
         <v>231</v>
       </c>
       <c r="E295" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F295">
         <v>2.0</v>
@@ -10787,47 +10802,47 @@
         <v>102</v>
       </c>
       <c r="I295" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B296" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C296" t="s">
         <v>474</v>
       </c>
       <c r="E296" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F296">
         <v>12.0</v>
       </c>
       <c r="G296" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H296" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="I296" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B297" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C297" t="s">
         <v>474</v>
       </c>
       <c r="E297" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F297">
         <v>10.0</v>
@@ -10836,70 +10851,70 @@
         <v>329</v>
       </c>
       <c r="H297" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I297" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B298" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C298" t="s">
         <v>401</v>
       </c>
       <c r="E298" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F298">
         <v>4.0</v>
       </c>
       <c r="G298" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H298" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I298" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B299" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C299" t="s">
         <v>401</v>
       </c>
       <c r="E299" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F299">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G299" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H299" t="s">
-        <v>644</v>
+        <v>746</v>
       </c>
       <c r="I299" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B300" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C300">
         <v>38</v>
@@ -10922,42 +10937,42 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B301" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C301" t="s">
         <v>231</v>
       </c>
       <c r="E301" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F301">
         <v>1.0</v>
       </c>
       <c r="G301" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H301" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I301" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B302" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C302" t="s">
         <v>151</v>
       </c>
       <c r="E302" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F302">
         <v>2.0</v>
@@ -10969,73 +10984,73 @@
         <v>102</v>
       </c>
       <c r="I302" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B303" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C303" t="s">
         <v>501</v>
       </c>
       <c r="E303" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F303">
         <v>2.0</v>
       </c>
       <c r="G303" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H303" t="s">
         <v>113</v>
       </c>
       <c r="I303" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B304" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C304" t="s">
         <v>401</v>
       </c>
       <c r="E304" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F304">
         <v>4.0</v>
       </c>
       <c r="G304" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H304" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="I304" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B305" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C305" t="s">
         <v>401</v>
       </c>
       <c r="E305" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F305">
         <v>5.0</v>
@@ -11047,15 +11062,15 @@
         <v>102</v>
       </c>
       <c r="I305" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B306" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C306" t="s">
         <v>123</v>
@@ -11067,10 +11082,10 @@
         <v>7.0</v>
       </c>
       <c r="G306" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="H306" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="I306" t="s">
         <v>281</v>
@@ -11078,25 +11093,25 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B307" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C307" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E307" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F307">
         <v>7.0</v>
       </c>
       <c r="G307" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="H307" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="I307" t="s">
         <v>434</v>
@@ -11104,16 +11119,16 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B308" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C308" t="s">
         <v>401</v>
       </c>
       <c r="E308" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F308">
         <v>6.0</v>
@@ -11125,15 +11140,15 @@
         <v>102</v>
       </c>
       <c r="I308" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="B309" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C309">
         <v>40</v>
@@ -11156,10 +11171,10 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B310" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C310">
         <v>42</v>
@@ -11182,36 +11197,36 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B311" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C311" t="s">
         <v>520</v>
       </c>
       <c r="E311" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F311">
         <v>7.0</v>
       </c>
       <c r="G311" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="H311" t="s">
         <v>420</v>
       </c>
       <c r="I311" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B312" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E312" t="s">
         <v>284</v>
@@ -11226,15 +11241,15 @@
         <v>149</v>
       </c>
       <c r="I312" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B313" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="E313" t="s">
         <v>284</v>
@@ -11254,16 +11269,16 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B314" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C314" t="s">
         <v>401</v>
       </c>
       <c r="E314" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F314">
         <v>3.0</v>
@@ -11275,15 +11290,15 @@
         <v>102</v>
       </c>
       <c r="I314" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B315" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C315" t="s">
         <v>501</v>
@@ -11295,21 +11310,21 @@
         <v>2.0</v>
       </c>
       <c r="G315" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="H315" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="I315" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B316" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C316" t="s">
         <v>231</v>
@@ -11332,88 +11347,88 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B317" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C317" t="s">
         <v>520</v>
       </c>
       <c r="E317" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F317">
         <v>5.0</v>
       </c>
       <c r="G317" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H317" t="s">
         <v>53</v>
       </c>
       <c r="I317" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B318" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C318" t="s">
         <v>520</v>
       </c>
       <c r="E318" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F318">
         <v>7.0</v>
       </c>
       <c r="G318" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="H318" t="s">
         <v>53</v>
       </c>
       <c r="I318" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B319" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C319" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E319" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F319">
         <v>4.0</v>
       </c>
       <c r="G319" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H319" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="I319" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B320" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C320" t="s">
         <v>136</v>
@@ -11425,27 +11440,27 @@
         <v>3.0</v>
       </c>
       <c r="G320" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H320" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="I320" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B321" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C321" t="s">
         <v>474</v>
       </c>
       <c r="E321" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F321">
         <v>1.0</v>
@@ -11457,47 +11472,47 @@
         <v>102</v>
       </c>
       <c r="I321" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B322" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C322" t="s">
         <v>501</v>
       </c>
       <c r="E322" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F322">
         <v>2.0</v>
       </c>
       <c r="G322" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H322" t="s">
         <v>113</v>
       </c>
       <c r="I322" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B323" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C323" t="s">
         <v>474</v>
       </c>
       <c r="E323" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F323">
         <v>2.0</v>
@@ -11506,24 +11521,24 @@
         <v>389</v>
       </c>
       <c r="H323" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="I323" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B324" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C324" t="s">
         <v>474</v>
       </c>
       <c r="E324" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F324">
         <v>2.0</v>
@@ -11532,24 +11547,24 @@
         <v>113</v>
       </c>
       <c r="H324" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I324" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B325" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C325" t="s">
         <v>401</v>
       </c>
       <c r="E325" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F325">
         <v>3.0</v>
@@ -11558,24 +11573,24 @@
         <v>389</v>
       </c>
       <c r="H325" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I325" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B326" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C326" t="s">
         <v>151</v>
       </c>
       <c r="E326" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F326">
         <v>3.0</v>
@@ -11587,27 +11602,27 @@
         <v>102</v>
       </c>
       <c r="I326" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B327" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C327" t="s">
         <v>401</v>
       </c>
       <c r="E327" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F327">
         <v>6.0</v>
       </c>
       <c r="G327" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H327" t="s">
         <v>420</v>
@@ -11618,36 +11633,36 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B328" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C328" t="s">
         <v>231</v>
       </c>
       <c r="E328" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F328">
         <v>4.0</v>
       </c>
       <c r="G328" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H328" t="s">
         <v>403</v>
       </c>
       <c r="I328" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B329" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C329" t="s">
         <v>151</v>
@@ -11659,27 +11674,27 @@
         <v>1.0</v>
       </c>
       <c r="G329" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="H329" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="I329" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B330" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C330" t="s">
         <v>136</v>
       </c>
       <c r="E330" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F330">
         <v>1.0</v>
@@ -11691,30 +11706,30 @@
         <v>102</v>
       </c>
       <c r="I330" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B331" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C331" t="s">
         <v>520</v>
       </c>
       <c r="E331" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F331">
         <v>5.0</v>
       </c>
       <c r="G331" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H331" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="I331" t="s">
         <v>280</v>
@@ -11722,16 +11737,16 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B332" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C332" t="s">
         <v>401</v>
       </c>
       <c r="E332" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F332">
         <v>5.0</v>
@@ -11743,15 +11758,15 @@
         <v>102</v>
       </c>
       <c r="I332" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B333" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C333">
         <v>44</v>
@@ -11774,16 +11789,16 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B334" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C334" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E334" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F334">
         <v>3.0</v>
@@ -11795,21 +11810,21 @@
         <v>102</v>
       </c>
       <c r="I334" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B335" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C335" t="s">
         <v>520</v>
       </c>
       <c r="E335" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F335">
         <v>3.0</v>
@@ -11818,24 +11833,24 @@
         <v>403</v>
       </c>
       <c r="H335" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I335" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B336" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C336" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E336" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F336">
         <v>4.0</v>
@@ -11847,21 +11862,21 @@
         <v>102</v>
       </c>
       <c r="I336" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B337" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C337" t="s">
         <v>520</v>
       </c>
       <c r="E337" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F337">
         <v>4.0</v>
@@ -11873,18 +11888,18 @@
         <v>102</v>
       </c>
       <c r="I337" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B338" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E338" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="F338">
         <v>1.0</v>
@@ -11896,15 +11911,15 @@
         <v>102</v>
       </c>
       <c r="I338" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="B339" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="E339" t="s">
         <v>284</v>
@@ -11916,50 +11931,50 @@
         <v>258</v>
       </c>
       <c r="H339" t="s">
-        <v>483</v>
+        <v>624</v>
       </c>
       <c r="I339" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B340" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C340" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E340" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F340">
         <v>4.0</v>
       </c>
       <c r="G340" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H340" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I340" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B341" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C341" t="s">
         <v>128</v>
       </c>
       <c r="E341" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F341">
         <v>10.0</v>
@@ -11971,47 +11986,47 @@
         <v>102</v>
       </c>
       <c r="I341" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B342" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C342" t="s">
         <v>501</v>
       </c>
       <c r="E342" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F342">
         <v>2.0</v>
       </c>
       <c r="G342" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H342" t="s">
         <v>113</v>
       </c>
       <c r="I342" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B343" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C343" t="s">
         <v>501</v>
       </c>
       <c r="E343" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F343">
         <v>2.0</v>
@@ -12020,96 +12035,96 @@
         <v>403</v>
       </c>
       <c r="H343" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I343" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B344" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C344" t="s">
         <v>474</v>
       </c>
       <c r="E344" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F344">
         <v>12.0</v>
       </c>
       <c r="G344" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H344" t="s">
         <v>156</v>
       </c>
       <c r="I344" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B345" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C345" t="s">
         <v>520</v>
       </c>
       <c r="E345" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F345">
         <v>6.0</v>
       </c>
       <c r="G345" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="H345" t="s">
         <v>341</v>
       </c>
       <c r="I345" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B346" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C346" t="s">
         <v>401</v>
       </c>
       <c r="E346" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F346">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G346" t="s">
         <v>530</v>
       </c>
       <c r="H346" t="s">
-        <v>53</v>
+        <v>531</v>
       </c>
       <c r="I346" t="s">
-        <v>454</v>
+        <v>772</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B347" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C347" t="s">
         <v>231</v>
@@ -12121,10 +12136,10 @@
         <v>1.0</v>
       </c>
       <c r="G347" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="H347" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="I347" t="s">
         <v>386</v>
@@ -12132,42 +12147,42 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B348" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C348" t="s">
         <v>401</v>
       </c>
       <c r="E348" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F348">
         <v>11.0</v>
       </c>
       <c r="G348" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="H348" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I348" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B349" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C349" t="s">
         <v>401</v>
       </c>
       <c r="E349" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F349">
         <v>4.0</v>
@@ -12179,21 +12194,21 @@
         <v>420</v>
       </c>
       <c r="I349" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B350" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C350" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E350" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F350">
         <v>1.0</v>
@@ -12205,41 +12220,41 @@
         <v>522</v>
       </c>
       <c r="I350" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B351" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C351" t="s">
         <v>401</v>
       </c>
       <c r="E351" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F351">
         <v>4.0</v>
       </c>
       <c r="G351" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H351" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I351" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B352" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C352" t="s">
         <v>136</v>
@@ -12262,94 +12277,94 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B353" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C353" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E353" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F353">
         <v>7.0</v>
       </c>
       <c r="G353" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="H353" t="s">
         <v>155</v>
       </c>
       <c r="I353" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B354" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C354" t="s">
         <v>474</v>
       </c>
       <c r="E354" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F354">
         <v>8.0</v>
       </c>
       <c r="G354" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="H354" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="I354" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B355" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C355" t="s">
         <v>520</v>
       </c>
       <c r="E355" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F355">
         <v>1.0</v>
       </c>
       <c r="G355" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H355" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I355" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B356" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C356" t="s">
         <v>520</v>
       </c>
       <c r="E356" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F356">
         <v>3.0</v>
@@ -12361,21 +12376,21 @@
         <v>102</v>
       </c>
       <c r="I356" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B357" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C357" t="s">
         <v>474</v>
       </c>
       <c r="E357" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F357">
         <v>2.0</v>
@@ -12384,24 +12399,24 @@
         <v>113</v>
       </c>
       <c r="H357" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I357" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B358" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C358" t="s">
         <v>128</v>
       </c>
       <c r="E358" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F358">
         <v>7.0</v>
@@ -12413,15 +12428,15 @@
         <v>102</v>
       </c>
       <c r="I358" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="359" spans="1:9">
       <c r="A359" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B359" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C359" t="s">
         <v>231</v>
@@ -12439,21 +12454,21 @@
         <v>102</v>
       </c>
       <c r="I359" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B360" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C360" t="s">
         <v>520</v>
       </c>
       <c r="E360" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F360">
         <v>6.0</v>
@@ -12465,21 +12480,21 @@
         <v>102</v>
       </c>
       <c r="I360" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B361" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C361" t="s">
         <v>128</v>
       </c>
       <c r="E361" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F361">
         <v>6.0</v>
@@ -12496,16 +12511,16 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B362" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C362" t="s">
         <v>151</v>
       </c>
       <c r="E362" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F362">
         <v>7.0</v>
@@ -12517,21 +12532,21 @@
         <v>102</v>
       </c>
       <c r="I362" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B363" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C363" t="s">
         <v>128</v>
       </c>
       <c r="E363" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F363">
         <v>7.0</v>
@@ -12543,21 +12558,21 @@
         <v>102</v>
       </c>
       <c r="I363" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B364" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C364" t="s">
         <v>501</v>
       </c>
       <c r="E364" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F364">
         <v>2.0</v>
@@ -12566,10 +12581,10 @@
         <v>403</v>
       </c>
       <c r="H364" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="I364" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -12589,10 +12604,10 @@
         <v>2.0</v>
       </c>
       <c r="G365" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="H365" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I365" t="s">
         <v>438</v>
@@ -12600,25 +12615,25 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B366" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C366" t="s">
         <v>520</v>
       </c>
       <c r="E366" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F366">
         <v>5.0</v>
       </c>
       <c r="G366" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="H366" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="I366" t="s">
         <v>280</v>
@@ -12626,42 +12641,42 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B367" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C367" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E367" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F367">
         <v>1.0</v>
       </c>
       <c r="G367" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H367" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I367" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B368" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C368" t="s">
         <v>474</v>
       </c>
       <c r="E368" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F368">
         <v>1.0</v>
@@ -12678,16 +12693,16 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B369" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C369" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E369" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F369">
         <v>1.0</v>
@@ -12699,15 +12714,15 @@
         <v>102</v>
       </c>
       <c r="I369" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B370" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C370" t="s">
         <v>231</v>
@@ -12725,47 +12740,47 @@
         <v>102</v>
       </c>
       <c r="I370" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B371" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C371" t="s">
         <v>401</v>
       </c>
       <c r="E371" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F371">
         <v>3.0</v>
       </c>
       <c r="G371" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="H371" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="I371" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B372" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C372" t="s">
         <v>128</v>
       </c>
       <c r="E372" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F372">
         <v>7.0</v>
@@ -12777,125 +12792,125 @@
         <v>102</v>
       </c>
       <c r="I372" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B373" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C373" t="s">
         <v>474</v>
       </c>
       <c r="E373" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F373">
         <v>10.0</v>
       </c>
       <c r="G373" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H373" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I373" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B374" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C374" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E374" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F374">
         <v>1.0</v>
       </c>
       <c r="G374" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H374" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I374" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B375" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C375" t="s">
         <v>231</v>
       </c>
       <c r="E375" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F375">
         <v>1.0</v>
       </c>
       <c r="G375" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="H375" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="I375" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B376" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C376" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E376" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F376">
         <v>9.0</v>
       </c>
       <c r="G376" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="H376" t="s">
         <v>420</v>
       </c>
       <c r="I376" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B377" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C377" t="s">
         <v>520</v>
       </c>
       <c r="E377" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F377">
         <v>2.0</v>
@@ -12907,15 +12922,15 @@
         <v>102</v>
       </c>
       <c r="I377" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="B378" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C378">
         <v>46</v>
@@ -12938,16 +12953,16 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B379" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C379" t="s">
         <v>128</v>
       </c>
       <c r="E379" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F379">
         <v>4.0</v>
@@ -12959,15 +12974,15 @@
         <v>102</v>
       </c>
       <c r="I379" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="380" spans="1:9">
       <c r="A380" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B380" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C380" t="s">
         <v>123</v>
@@ -12985,47 +13000,47 @@
         <v>102</v>
       </c>
       <c r="I380" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B381" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C381" t="s">
         <v>474</v>
       </c>
       <c r="E381" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F381">
         <v>9.0</v>
       </c>
       <c r="G381" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="H381" t="s">
         <v>259</v>
       </c>
       <c r="I381" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B382" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C382" t="s">
         <v>128</v>
       </c>
       <c r="E382" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F382">
         <v>7.0</v>
@@ -13037,21 +13052,21 @@
         <v>102</v>
       </c>
       <c r="I382" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B383" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C383" t="s">
         <v>520</v>
       </c>
       <c r="E383" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F383">
         <v>1.0</v>
@@ -13063,21 +13078,21 @@
         <v>113</v>
       </c>
       <c r="I383" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B384" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C384" t="s">
         <v>520</v>
       </c>
       <c r="E384" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F384">
         <v>2.0</v>
@@ -13086,50 +13101,50 @@
         <v>113</v>
       </c>
       <c r="H384" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I384" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B385" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C385" t="s">
         <v>401</v>
       </c>
       <c r="E385" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F385">
         <v>2.0</v>
       </c>
       <c r="G385" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H385" t="s">
         <v>113</v>
       </c>
       <c r="I385" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B386" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C386" t="s">
         <v>401</v>
       </c>
       <c r="E386" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F386">
         <v>1.0</v>
@@ -13141,21 +13156,21 @@
         <v>113</v>
       </c>
       <c r="I386" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="387" spans="1:9">
       <c r="A387" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B387" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C387" t="s">
         <v>231</v>
       </c>
       <c r="E387" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F387">
         <v>8.0</v>
@@ -13167,15 +13182,15 @@
         <v>102</v>
       </c>
       <c r="I387" t="s">
-        <v>742</v>
+        <v>852</v>
       </c>
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B388" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C388" t="s">
         <v>123</v>
@@ -13193,47 +13208,47 @@
         <v>102</v>
       </c>
       <c r="I388" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B389" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C389" t="s">
         <v>123</v>
       </c>
       <c r="E389" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F389">
         <v>5.0</v>
       </c>
       <c r="G389" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="H389" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="I389" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B390" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C390" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E390" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F390">
         <v>5.0</v>
@@ -13245,47 +13260,47 @@
         <v>102</v>
       </c>
       <c r="I390" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B391" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C391" t="s">
         <v>474</v>
       </c>
       <c r="E391" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F391">
         <v>1.0</v>
       </c>
       <c r="G391" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H391" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I391" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B392" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C392" t="s">
         <v>123</v>
       </c>
       <c r="E392" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F392">
         <v>10.0</v>
@@ -13297,15 +13312,15 @@
         <v>102</v>
       </c>
       <c r="I392" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B393" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C393" t="s">
         <v>123</v>
@@ -13328,16 +13343,16 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B394" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C394" t="s">
         <v>128</v>
       </c>
       <c r="E394" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F394">
         <v>4.0</v>
@@ -13349,21 +13364,21 @@
         <v>102</v>
       </c>
       <c r="I394" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B395" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C395" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E395" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F395">
         <v>2.0</v>
@@ -13372,24 +13387,24 @@
         <v>113</v>
       </c>
       <c r="H395" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="I395" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B396" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C396" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E396" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F396">
         <v>1.0</v>
@@ -13401,21 +13416,21 @@
         <v>102</v>
       </c>
       <c r="I396" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B397" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C397" t="s">
         <v>520</v>
       </c>
       <c r="E397" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F397">
         <v>1.0</v>
@@ -13427,21 +13442,21 @@
         <v>113</v>
       </c>
       <c r="I397" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B398" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C398" t="s">
         <v>401</v>
       </c>
       <c r="E398" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F398">
         <v>2.0</v>
@@ -13453,41 +13468,41 @@
         <v>102</v>
       </c>
       <c r="I398" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B399" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C399" t="s">
         <v>401</v>
       </c>
       <c r="E399" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F399">
         <v>1.0</v>
       </c>
       <c r="G399" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H399" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I399" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B400" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C400" t="s">
         <v>123</v>
@@ -13510,16 +13525,16 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B401" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C401" t="s">
         <v>128</v>
       </c>
       <c r="E401" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F401">
         <v>5.0</v>
@@ -13531,21 +13546,21 @@
         <v>102</v>
       </c>
       <c r="I401" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B402" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C402" t="s">
         <v>123</v>
       </c>
       <c r="E402" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F402">
         <v>16.0</v>
@@ -13557,21 +13572,21 @@
         <v>102</v>
       </c>
       <c r="I402" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B403" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C403" t="s">
         <v>501</v>
       </c>
       <c r="E403" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F403">
         <v>2.0</v>
@@ -13583,99 +13598,99 @@
         <v>102</v>
       </c>
       <c r="I403" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="B404" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C404" t="s">
         <v>474</v>
       </c>
       <c r="E404" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F404">
         <v>1.0</v>
       </c>
       <c r="G404" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H404" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I404" t="s">
-        <v>102</v>
+        <v>665</v>
       </c>
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B405" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C405" t="s">
         <v>474</v>
       </c>
       <c r="E405" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F405">
         <v>2.0</v>
       </c>
       <c r="G405" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="H405" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I405" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B406" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C406" t="s">
         <v>401</v>
       </c>
       <c r="E406" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F406">
         <v>3.0</v>
       </c>
       <c r="G406" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="H406" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I406" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B407" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C407" t="s">
         <v>474</v>
       </c>
       <c r="E407" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F407">
         <v>2.0</v>
@@ -13687,15 +13702,15 @@
         <v>102</v>
       </c>
       <c r="I407" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="408" spans="1:9">
       <c r="A408" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B408" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C408" t="s">
         <v>151</v>
@@ -13713,21 +13728,21 @@
         <v>102</v>
       </c>
       <c r="I408" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B409" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C409" t="s">
         <v>151</v>
       </c>
       <c r="E409" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F409">
         <v>8.0</v>
@@ -13739,21 +13754,21 @@
         <v>102</v>
       </c>
       <c r="I409" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B410" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C410" t="s">
         <v>231</v>
       </c>
       <c r="E410" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F410">
         <v>6.0</v>
@@ -13765,21 +13780,21 @@
         <v>102</v>
       </c>
       <c r="I410" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="411" spans="1:9">
       <c r="A411" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B411" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C411" t="s">
         <v>501</v>
       </c>
       <c r="E411" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F411">
         <v>1.0</v>
@@ -13791,21 +13806,21 @@
         <v>102</v>
       </c>
       <c r="I411" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B412" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C412" t="s">
         <v>151</v>
       </c>
       <c r="E412" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F412">
         <v>9.0</v>
@@ -13817,15 +13832,15 @@
         <v>102</v>
       </c>
       <c r="I412" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B413" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C413" t="s">
         <v>136</v>
@@ -13843,21 +13858,21 @@
         <v>102</v>
       </c>
       <c r="I413" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
     </row>
     <row r="414" spans="1:9">
       <c r="A414" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B414" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C414" t="s">
         <v>151</v>
       </c>
       <c r="E414" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F414">
         <v>9.0</v>
@@ -13869,21 +13884,21 @@
         <v>102</v>
       </c>
       <c r="I414" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="415" spans="1:9">
       <c r="A415" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B415" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C415" t="s">
         <v>123</v>
       </c>
       <c r="E415" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F415">
         <v>4.0</v>
@@ -13895,21 +13910,21 @@
         <v>102</v>
       </c>
       <c r="I415" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="416" spans="1:9">
       <c r="A416" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B416" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C416" t="s">
         <v>474</v>
       </c>
       <c r="E416" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F416">
         <v>4.0</v>
@@ -13921,41 +13936,41 @@
         <v>102</v>
       </c>
       <c r="I416" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B417" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C417" t="s">
         <v>501</v>
       </c>
       <c r="E417" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F417">
         <v>1.0</v>
       </c>
       <c r="G417" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H417" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I417" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="418" spans="1:9">
       <c r="A418" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B418" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C418" t="s">
         <v>151</v>
@@ -13978,16 +13993,16 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B419" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C419" t="s">
         <v>128</v>
       </c>
       <c r="E419" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F419">
         <v>7.0</v>
@@ -13999,15 +14014,15 @@
         <v>102</v>
       </c>
       <c r="I419" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B420" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C420" t="s">
         <v>128</v>
@@ -14030,10 +14045,10 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B421" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C421" t="s">
         <v>136</v>
@@ -14051,15 +14066,15 @@
         <v>102</v>
       </c>
       <c r="I421" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="422" spans="1:9">
       <c r="A422" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B422" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C422" t="s">
         <v>136</v>
@@ -14071,27 +14086,27 @@
         <v>11.0</v>
       </c>
       <c r="G422" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H422" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="I422" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="423" spans="1:9">
       <c r="A423" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B423" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C423" t="s">
         <v>136</v>
       </c>
       <c r="E423" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F423">
         <v>15.0</v>
@@ -14103,15 +14118,15 @@
         <v>102</v>
       </c>
       <c r="I423" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="424" spans="1:9">
       <c r="A424" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B424" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C424" t="s">
         <v>151</v>
@@ -14134,16 +14149,16 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B425" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C425" t="s">
         <v>501</v>
       </c>
       <c r="E425" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F425">
         <v>1.0</v>
@@ -14155,21 +14170,21 @@
         <v>102</v>
       </c>
       <c r="I425" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B426" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C426" t="s">
         <v>136</v>
       </c>
       <c r="E426" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F426">
         <v>17.0</v>
@@ -14181,21 +14196,21 @@
         <v>102</v>
       </c>
       <c r="I426" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B427" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C427" t="s">
         <v>123</v>
       </c>
       <c r="E427" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F427">
         <v>19.0</v>
@@ -14207,73 +14222,73 @@
         <v>102</v>
       </c>
       <c r="I427" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
     </row>
     <row r="428" spans="1:9">
       <c r="A428" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B428" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C428" t="s">
         <v>520</v>
       </c>
       <c r="E428" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F428">
         <v>2.0</v>
       </c>
       <c r="G428" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H428" t="s">
         <v>113</v>
       </c>
       <c r="I428" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B429" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C429" t="s">
         <v>501</v>
       </c>
       <c r="E429" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F429">
         <v>2.0</v>
       </c>
       <c r="G429" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H429" t="s">
         <v>113</v>
       </c>
       <c r="I429" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B430" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C430" t="s">
         <v>474</v>
       </c>
       <c r="E430" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F430">
         <v>1.0</v>
@@ -14290,16 +14305,16 @@
     </row>
     <row r="431" spans="1:9">
       <c r="A431" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B431" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C431" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E431" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F431">
         <v>2.0</v>
@@ -14311,21 +14326,21 @@
         <v>102</v>
       </c>
       <c r="I431" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="432" spans="1:9">
       <c r="A432" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B432" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C432" t="s">
         <v>520</v>
       </c>
       <c r="E432" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F432">
         <v>1.0</v>
@@ -14342,16 +14357,16 @@
     </row>
     <row r="433" spans="1:9">
       <c r="A433" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B433" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C433" t="s">
         <v>401</v>
       </c>
       <c r="E433" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F433">
         <v>1.0</v>
@@ -14368,16 +14383,16 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B434" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C434" t="s">
         <v>520</v>
       </c>
       <c r="E434" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F434">
         <v>1.0</v>
@@ -14394,10 +14409,10 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B435" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C435" t="s">
         <v>128</v>
@@ -14415,15 +14430,15 @@
         <v>102</v>
       </c>
       <c r="I435" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B436" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C436" t="s">
         <v>123</v>
@@ -14446,10 +14461,10 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B437" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C437" t="s">
         <v>231</v>
@@ -14461,10 +14476,10 @@
         <v>3.0</v>
       </c>
       <c r="G437" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="H437" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="I437" t="s">
         <v>342</v>
@@ -14472,10 +14487,10 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B438" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C438" t="s">
         <v>136</v>
@@ -14487,7 +14502,7 @@
         <v>12.0</v>
       </c>
       <c r="G438" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="H438" t="s">
         <v>291</v>
@@ -14498,10 +14513,10 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B439" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C439" t="s">
         <v>151</v>
@@ -14513,27 +14528,27 @@
         <v>3.0</v>
       </c>
       <c r="G439" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="H439" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="I439" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B440" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C440" t="s">
         <v>136</v>
       </c>
       <c r="E440" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F440">
         <v>7.0</v>
@@ -14545,21 +14560,21 @@
         <v>102</v>
       </c>
       <c r="I440" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B441" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C441" t="s">
         <v>520</v>
       </c>
       <c r="E441" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F441">
         <v>1.0</v>
@@ -14571,41 +14586,41 @@
         <v>102</v>
       </c>
       <c r="I441" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="B442" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C442" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E442" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F442">
         <v>1.0</v>
       </c>
       <c r="G442" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H442" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I442" t="s">
-        <v>102</v>
+        <v>665</v>
       </c>
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B443" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C443" t="s">
         <v>136</v>
@@ -14623,15 +14638,15 @@
         <v>102</v>
       </c>
       <c r="I443" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B444" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C444" t="s">
         <v>136</v>
@@ -14649,21 +14664,21 @@
         <v>102</v>
       </c>
       <c r="I444" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B445" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C445" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E445" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F445">
         <v>2.0</v>
@@ -14675,21 +14690,21 @@
         <v>102</v>
       </c>
       <c r="I445" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B446" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C446" t="s">
         <v>501</v>
       </c>
       <c r="E446" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F446">
         <v>1.0</v>
@@ -14701,21 +14716,21 @@
         <v>102</v>
       </c>
       <c r="I446" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B447" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C447" t="s">
         <v>401</v>
       </c>
       <c r="E447" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F447">
         <v>1.0</v>
@@ -14732,16 +14747,16 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B448" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C448" t="s">
         <v>501</v>
       </c>
       <c r="E448" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F448">
         <v>1.0</v>
@@ -14758,42 +14773,42 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B449" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C449" t="s">
         <v>474</v>
       </c>
       <c r="E449" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F449">
         <v>1.0</v>
       </c>
       <c r="G449" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H449" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I449" t="s">
-        <v>102</v>
+        <v>845</v>
       </c>
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B450" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C450" t="s">
         <v>123</v>
       </c>
       <c r="E450" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F450">
         <v>10.0</v>
@@ -14805,12 +14820,12 @@
         <v>102</v>
       </c>
       <c r="I450" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B451" t="s">
         <v>68</v>
@@ -14831,18 +14846,18 @@
         <v>102</v>
       </c>
       <c r="I451" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="B452" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E452" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="F452">
         <v>1.0</v>
@@ -14859,13 +14874,13 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B453" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E453" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="F453">
         <v>1.0</v>
@@ -14882,16 +14897,16 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="B454" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C454" t="s">
         <v>151</v>
       </c>
       <c r="E454" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F454">
         <v>1.0</v>
@@ -14934,10 +14949,10 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B456" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C456" t="s">
         <v>231</v>
@@ -14960,10 +14975,10 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B457" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C457" t="s">
         <v>136</v>
@@ -14986,10 +15001,10 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B458" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C458" t="s">
         <v>123</v>
@@ -15007,15 +15022,15 @@
         <v>102</v>
       </c>
       <c r="I458" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="459" spans="1:9">
       <c r="A459" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B459" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C459" t="s">
         <v>151</v>
@@ -15038,10 +15053,10 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B460" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C460" t="s">
         <v>123</v>
@@ -15059,15 +15074,15 @@
         <v>102</v>
       </c>
       <c r="I460" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="461" spans="1:9">
       <c r="A461" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B461" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C461" t="s">
         <v>151</v>
@@ -15085,15 +15100,15 @@
         <v>102</v>
       </c>
       <c r="I461" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="462" spans="1:9">
       <c r="A462" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B462" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C462" t="s">
         <v>151</v>
@@ -15111,15 +15126,15 @@
         <v>102</v>
       </c>
       <c r="I462" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="463" spans="1:9">
       <c r="A463" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="B463" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="C463" t="s">
         <v>151</v>
@@ -15142,10 +15157,10 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B464" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C464" t="s">
         <v>151</v>
@@ -15168,10 +15183,10 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B465" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C465" t="s">
         <v>128</v>
@@ -15189,15 +15204,15 @@
         <v>102</v>
       </c>
       <c r="I465" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="466" spans="1:9">
       <c r="A466" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B466" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C466" t="s">
         <v>128</v>
@@ -15215,15 +15230,15 @@
         <v>102</v>
       </c>
       <c r="I466" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B467" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C467" t="s">
         <v>123</v>
@@ -15241,15 +15256,15 @@
         <v>102</v>
       </c>
       <c r="I467" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="468" spans="1:9">
       <c r="A468" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B468" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C468" t="s">
         <v>128</v>
@@ -15272,16 +15287,16 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B469" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C469" t="s">
         <v>136</v>
       </c>
       <c r="E469" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F469">
         <v>15.0</v>
@@ -15293,21 +15308,21 @@
         <v>102</v>
       </c>
       <c r="I469" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="470" spans="1:9">
       <c r="A470" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B470" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C470" t="s">
         <v>123</v>
       </c>
       <c r="E470" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F470">
         <v>17.0</v>
@@ -15319,21 +15334,21 @@
         <v>102</v>
       </c>
       <c r="I470" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="471" spans="1:9">
       <c r="A471" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B471" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C471" t="s">
         <v>136</v>
       </c>
       <c r="E471" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F471">
         <v>10.0</v>
@@ -15345,21 +15360,21 @@
         <v>102</v>
       </c>
       <c r="I471" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="472" spans="1:9">
       <c r="A472" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B472" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C472" t="s">
         <v>151</v>
       </c>
       <c r="E472" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F472">
         <v>5.0</v>
@@ -15371,21 +15386,21 @@
         <v>102</v>
       </c>
       <c r="I472" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="473" spans="1:9">
       <c r="A473" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B473" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C473" t="s">
         <v>123</v>
       </c>
       <c r="E473" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F473">
         <v>10.0</v>
@@ -15397,18 +15412,18 @@
         <v>102</v>
       </c>
       <c r="I473" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="474" spans="1:9">
       <c r="A474" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="B474" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="E474" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F474">
         <v>2.0</v>
@@ -15425,13 +15440,13 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="B475" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="E475" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F475">
         <v>3.0</v>
@@ -15448,13 +15463,13 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="B476" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="E476" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F476">
         <v>1.0</v>
@@ -15466,18 +15481,18 @@
         <v>102</v>
       </c>
       <c r="I476" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
     </row>
     <row r="477" spans="1:9">
       <c r="A477" t="s">
+        <v>920</v>
+      </c>
+      <c r="B477" t="s">
+        <v>921</v>
+      </c>
+      <c r="E477" t="s">
         <v>915</v>
-      </c>
-      <c r="B477" t="s">
-        <v>916</v>
-      </c>
-      <c r="E477" t="s">
-        <v>910</v>
       </c>
       <c r="F477">
         <v>2.0</v>
@@ -15494,13 +15509,13 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="B478" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="E478" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F478">
         <v>3.0</v>
@@ -15512,7 +15527,7 @@
         <v>102</v>
       </c>
       <c r="I478" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="479" spans="1:9">
@@ -15543,16 +15558,16 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B480" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C480" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E480" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F480">
         <v>1.0</v>
@@ -15564,15 +15579,15 @@
         <v>102</v>
       </c>
       <c r="I480" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="481" spans="1:9">
       <c r="A481" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="B481" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="E481" t="s">
         <v>284</v>
@@ -15592,16 +15607,16 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B482" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C482" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E482" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F482">
         <v>6.0</v>
@@ -15613,21 +15628,21 @@
         <v>102</v>
       </c>
       <c r="I482" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="483" spans="1:9">
       <c r="A483" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B483" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C483" t="s">
         <v>474</v>
       </c>
       <c r="E483" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F483">
         <v>10.0</v>
@@ -15639,21 +15654,21 @@
         <v>102</v>
       </c>
       <c r="I483" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="484" spans="1:9">
       <c r="A484" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B484" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C484" t="s">
         <v>401</v>
       </c>
       <c r="E484" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F484">
         <v>7.0</v>
@@ -15665,21 +15680,21 @@
         <v>102</v>
       </c>
       <c r="I484" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="485" spans="1:9">
       <c r="A485" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B485" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C485" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E485" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F485">
         <v>6.0</v>
@@ -15691,21 +15706,21 @@
         <v>102</v>
       </c>
       <c r="I485" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="486" spans="1:9">
       <c r="A486" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B486" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C486" t="s">
         <v>474</v>
       </c>
       <c r="E486" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F486">
         <v>10.0</v>
@@ -15717,21 +15732,21 @@
         <v>102</v>
       </c>
       <c r="I486" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="487" spans="1:9">
       <c r="A487" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B487" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C487" t="s">
         <v>401</v>
       </c>
       <c r="E487" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F487">
         <v>7.0</v>
@@ -15743,21 +15758,21 @@
         <v>102</v>
       </c>
       <c r="I487" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="488" spans="1:9">
       <c r="A488" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B488" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C488" t="s">
         <v>520</v>
       </c>
       <c r="E488" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F488">
         <v>4.0</v>
@@ -15769,21 +15784,21 @@
         <v>102</v>
       </c>
       <c r="I488" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="489" spans="1:9">
       <c r="A489" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="B489" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C489" t="s">
         <v>501</v>
       </c>
       <c r="E489" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F489">
         <v>3.0</v>
@@ -15795,21 +15810,21 @@
         <v>102</v>
       </c>
       <c r="I489" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
     </row>
     <row r="490" spans="1:9">
       <c r="A490" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B490" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C490" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E490" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F490">
         <v>5.0</v>
@@ -15821,24 +15836,24 @@
         <v>102</v>
       </c>
       <c r="I490" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
     </row>
     <row r="491" spans="1:9">
       <c r="A491" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B491" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C491" t="s">
         <v>474</v>
       </c>
       <c r="E491" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F491">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G491" t="s">
         <v>102</v>
@@ -15847,21 +15862,21 @@
         <v>102</v>
       </c>
       <c r="I491" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="492" spans="1:9">
       <c r="A492" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B492" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C492" t="s">
         <v>401</v>
       </c>
       <c r="E492" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F492">
         <v>3.0</v>
@@ -15873,21 +15888,21 @@
         <v>102</v>
       </c>
       <c r="I492" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="493" spans="1:9">
       <c r="A493" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B493" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C493" t="s">
         <v>520</v>
       </c>
       <c r="E493" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F493">
         <v>4.0</v>
@@ -15899,21 +15914,21 @@
         <v>102</v>
       </c>
       <c r="I493" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="494" spans="1:9">
       <c r="A494" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B494" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C494" t="s">
         <v>501</v>
       </c>
       <c r="E494" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F494">
         <v>1.0</v>
@@ -15925,21 +15940,21 @@
         <v>102</v>
       </c>
       <c r="I494" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="495" spans="1:9">
       <c r="A495" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B495" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="C495" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E495" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F495">
         <v>2.0</v>
@@ -15951,21 +15966,21 @@
         <v>102</v>
       </c>
       <c r="I495" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="496" spans="1:9">
       <c r="A496" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B496" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="C496" t="s">
         <v>501</v>
       </c>
       <c r="E496" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F496">
         <v>3.0</v>
@@ -15982,16 +15997,16 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B497" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="C497" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E497" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F497">
         <v>4.0</v>
@@ -16003,21 +16018,21 @@
         <v>102</v>
       </c>
       <c r="I497" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="498" spans="1:9">
       <c r="A498" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B498" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="C498" t="s">
         <v>474</v>
       </c>
       <c r="E498" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F498">
         <v>4.0</v>
@@ -16029,21 +16044,21 @@
         <v>102</v>
       </c>
       <c r="I498" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="499" spans="1:9">
       <c r="A499" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B499" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="C499" t="s">
         <v>401</v>
       </c>
       <c r="E499" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F499">
         <v>1.0</v>
@@ -16060,16 +16075,16 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B500" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C500" t="s">
         <v>474</v>
       </c>
       <c r="E500" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F500">
         <v>4.0</v>
@@ -16081,21 +16096,21 @@
         <v>102</v>
       </c>
       <c r="I500" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="501" spans="1:9">
       <c r="A501" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B501" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C501" t="s">
         <v>401</v>
       </c>
       <c r="E501" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F501">
         <v>1.0</v>
@@ -16112,16 +16127,16 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B502" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C502" t="s">
         <v>520</v>
       </c>
       <c r="E502" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F502">
         <v>2.0</v>
@@ -16138,16 +16153,16 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B503" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C503" t="s">
         <v>501</v>
       </c>
       <c r="E503" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F503">
         <v>2.0</v>
@@ -16164,19 +16179,19 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="B504" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C504" t="s">
-        <v>474</v>
+        <v>401</v>
       </c>
       <c r="E504" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F504">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G504" t="s">
         <v>102</v>
@@ -16185,24 +16200,24 @@
         <v>102</v>
       </c>
       <c r="I504" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="505" spans="1:9">
       <c r="A505" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="B505" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C505" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="E505" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F505">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G505" t="s">
         <v>102</v>
@@ -16211,21 +16226,21 @@
         <v>102</v>
       </c>
       <c r="I505" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="B506" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C506" t="s">
         <v>501</v>
       </c>
       <c r="E506" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F506">
         <v>1.0</v>
@@ -16237,21 +16252,21 @@
         <v>102</v>
       </c>
       <c r="I506" t="s">
-        <v>934</v>
+        <v>62</v>
       </c>
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="B507" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="C507" t="s">
-        <v>520</v>
+        <v>596</v>
       </c>
       <c r="E507" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F507">
         <v>1.0</v>
@@ -16263,24 +16278,24 @@
         <v>102</v>
       </c>
       <c r="I507" t="s">
-        <v>62</v>
+        <v>952</v>
       </c>
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="B508" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="C508" t="s">
         <v>501</v>
       </c>
       <c r="E508" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F508">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G508" t="s">
         <v>102</v>
@@ -16289,21 +16304,21 @@
         <v>102</v>
       </c>
       <c r="I508" t="s">
-        <v>62</v>
+        <v>953</v>
       </c>
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="B509" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="C509" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E509" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F509">
         <v>1.0</v>
@@ -16315,24 +16330,24 @@
         <v>102</v>
       </c>
       <c r="I509" t="s">
-        <v>947</v>
+        <v>28</v>
       </c>
     </row>
     <row r="510" spans="1:9">
       <c r="A510" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="B510" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="C510" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="E510" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F510">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G510" t="s">
         <v>102</v>
@@ -16341,24 +16356,24 @@
         <v>102</v>
       </c>
       <c r="I510" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B511" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C511" t="s">
-        <v>595</v>
+        <v>401</v>
       </c>
       <c r="E511" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F511">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G511" t="s">
         <v>102</v>
@@ -16367,24 +16382,24 @@
         <v>102</v>
       </c>
       <c r="I511" t="s">
-        <v>28</v>
+        <v>956</v>
       </c>
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B512" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C512" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="E512" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F512">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G512" t="s">
         <v>102</v>
@@ -16393,24 +16408,24 @@
         <v>102</v>
       </c>
       <c r="I512" t="s">
-        <v>951</v>
+        <v>859</v>
       </c>
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B513" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C513" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="E513" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F513">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G513" t="s">
         <v>102</v>
@@ -16419,21 +16434,21 @@
         <v>102</v>
       </c>
       <c r="I513" t="s">
-        <v>951</v>
+        <v>859</v>
       </c>
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>949</v>
+        <v>874</v>
       </c>
       <c r="B514" t="s">
-        <v>950</v>
+        <v>875</v>
       </c>
       <c r="C514" t="s">
-        <v>520</v>
+        <v>401</v>
       </c>
       <c r="E514" t="s">
-        <v>827</v>
+        <v>635</v>
       </c>
       <c r="F514">
         <v>2.0</v>
@@ -16445,24 +16460,24 @@
         <v>102</v>
       </c>
       <c r="I514" t="s">
-        <v>854</v>
+        <v>704</v>
       </c>
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>949</v>
+        <v>865</v>
       </c>
       <c r="B515" t="s">
-        <v>950</v>
+        <v>866</v>
       </c>
       <c r="C515" t="s">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="E515" t="s">
-        <v>827</v>
+        <v>635</v>
       </c>
       <c r="F515">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G515" t="s">
         <v>102</v>
@@ -16471,24 +16486,24 @@
         <v>102</v>
       </c>
       <c r="I515" t="s">
-        <v>854</v>
+        <v>820</v>
       </c>
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="B516" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="C516" t="s">
-        <v>401</v>
+        <v>596</v>
       </c>
       <c r="E516" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F516">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G516" t="s">
         <v>102</v>
@@ -16497,21 +16512,21 @@
         <v>102</v>
       </c>
       <c r="I516" t="s">
-        <v>700</v>
+        <v>28</v>
       </c>
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="B517" t="s">
-        <v>861</v>
+        <v>885</v>
       </c>
       <c r="C517" t="s">
-        <v>595</v>
+        <v>501</v>
       </c>
       <c r="E517" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F517">
         <v>1.0</v>
@@ -16523,21 +16538,21 @@
         <v>102</v>
       </c>
       <c r="I517" t="s">
-        <v>816</v>
+        <v>28</v>
       </c>
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="B518" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="C518" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E518" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F518">
         <v>1.0</v>
@@ -16554,16 +16569,16 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>879</v>
+        <v>957</v>
       </c>
       <c r="B519" t="s">
-        <v>880</v>
+        <v>958</v>
       </c>
       <c r="C519" t="s">
-        <v>501</v>
+        <v>596</v>
       </c>
       <c r="E519" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F519">
         <v>1.0</v>
@@ -16575,24 +16590,24 @@
         <v>102</v>
       </c>
       <c r="I519" t="s">
-        <v>28</v>
+        <v>845</v>
       </c>
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="B520" t="s">
-        <v>865</v>
+        <v>958</v>
       </c>
       <c r="C520" t="s">
-        <v>595</v>
+        <v>474</v>
       </c>
       <c r="E520" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F520">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G520" t="s">
         <v>102</v>
@@ -16601,21 +16616,21 @@
         <v>102</v>
       </c>
       <c r="I520" t="s">
-        <v>28</v>
+        <v>704</v>
       </c>
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B521" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="C521" t="s">
-        <v>595</v>
+        <v>401</v>
       </c>
       <c r="E521" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F521">
         <v>1.0</v>
@@ -16627,24 +16642,24 @@
         <v>102</v>
       </c>
       <c r="I521" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="522" spans="1:9">
       <c r="A522" t="s">
-        <v>952</v>
+        <v>904</v>
       </c>
       <c r="B522" t="s">
-        <v>953</v>
+        <v>905</v>
       </c>
       <c r="C522" t="s">
-        <v>474</v>
+        <v>151</v>
       </c>
       <c r="E522" t="s">
-        <v>632</v>
+        <v>266</v>
       </c>
       <c r="F522">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G522" t="s">
         <v>102</v>
@@ -16653,24 +16668,24 @@
         <v>102</v>
       </c>
       <c r="I522" t="s">
-        <v>700</v>
+        <v>959</v>
       </c>
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="B523" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="C523" t="s">
-        <v>401</v>
+        <v>128</v>
       </c>
       <c r="E523" t="s">
-        <v>632</v>
+        <v>441</v>
       </c>
       <c r="F523">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G523" t="s">
         <v>102</v>
@@ -16679,24 +16694,24 @@
         <v>102</v>
       </c>
       <c r="I523" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>899</v>
+        <v>960</v>
       </c>
       <c r="B524" t="s">
-        <v>900</v>
+        <v>961</v>
       </c>
       <c r="C524" t="s">
         <v>151</v>
       </c>
       <c r="E524" t="s">
-        <v>266</v>
+        <v>441</v>
       </c>
       <c r="F524">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G524" t="s">
         <v>102</v>
@@ -16705,215 +16720,163 @@
         <v>102</v>
       </c>
       <c r="I524" t="s">
-        <v>954</v>
+        <v>606</v>
       </c>
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="B525" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="C525" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E525" t="s">
         <v>441</v>
       </c>
       <c r="F525">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G525" t="s">
-        <v>102</v>
+        <v>962</v>
       </c>
       <c r="H525" t="s">
-        <v>102</v>
+        <v>962</v>
       </c>
       <c r="I525" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="B526" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C526" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
       <c r="E526" t="s">
-        <v>441</v>
+        <v>831</v>
       </c>
       <c r="F526">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G526" t="s">
-        <v>102</v>
+        <v>965</v>
       </c>
       <c r="H526" t="s">
-        <v>102</v>
+        <v>966</v>
       </c>
       <c r="I526" t="s">
-        <v>605</v>
+        <v>937</v>
       </c>
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="B527" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C527" t="s">
-        <v>123</v>
+        <v>501</v>
       </c>
       <c r="E527" t="s">
-        <v>441</v>
+        <v>831</v>
       </c>
       <c r="F527">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G527" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="H527" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="I527" t="s">
-        <v>798</v>
+        <v>969</v>
       </c>
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="B528" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="C528" t="s">
-        <v>401</v>
+        <v>520</v>
       </c>
       <c r="E528" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F528">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G528" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="H528" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="I528" t="s">
-        <v>932</v>
+        <v>969</v>
       </c>
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="B529" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="C529" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="E529" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F529">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G529" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="H529" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="I529" t="s">
-        <v>964</v>
+        <v>938</v>
       </c>
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
-        <v>958</v>
+        <v>829</v>
       </c>
       <c r="B530" t="s">
-        <v>959</v>
+        <v>830</v>
       </c>
       <c r="C530" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="E530" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F530">
         <v>2.0</v>
       </c>
       <c r="G530" t="s">
-        <v>963</v>
+        <v>102</v>
       </c>
       <c r="H530" t="s">
-        <v>965</v>
+        <v>102</v>
       </c>
       <c r="I530" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="531" spans="1:9">
-      <c r="A531" t="s">
-        <v>958</v>
-      </c>
-      <c r="B531" t="s">
-        <v>959</v>
-      </c>
-      <c r="C531" t="s">
-        <v>474</v>
-      </c>
-      <c r="E531" t="s">
-        <v>827</v>
-      </c>
-      <c r="F531">
-        <v>4.0</v>
-      </c>
-      <c r="G531" t="s">
-        <v>963</v>
-      </c>
-      <c r="H531" t="s">
-        <v>966</v>
-      </c>
-      <c r="I531" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="532" spans="1:9">
-      <c r="A532" t="s">
-        <v>825</v>
-      </c>
-      <c r="B532" t="s">
-        <v>826</v>
-      </c>
-      <c r="C532" t="s">
-        <v>501</v>
-      </c>
-      <c r="E532" t="s">
-        <v>827</v>
-      </c>
-      <c r="F532">
-        <v>2.0</v>
-      </c>
-      <c r="G532" t="s">
-        <v>102</v>
-      </c>
-      <c r="H532" t="s">
-        <v>102</v>
-      </c>
-      <c r="I532" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
